--- a/Figures.out/gbr_out_sheep_hin.xlsx
+++ b/Figures.out/gbr_out_sheep_hin.xlsx
@@ -12,11 +12,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t xml:space="preserve">matrix.NA..nrow...n.rows..ncol...1.</t>
   </si>
   <si>
+    <t xml:space="preserve">loop.iter</t>
+  </si>
+  <si>
     <t xml:space="preserve">species</t>
   </si>
   <si>
@@ -290,40 +293,37 @@
     <t xml:space="preserve">1-1-1</t>
   </si>
   <si>
-    <t xml:space="preserve">858.58, 949.88, 938.04, 536, 691, 400, 462, 607, 361, 1472, 1433, 1415, 540.5, 788, 665.8, 1040.8, 1053, 890.2, 1030.4, 1339, 1201, 1152, 1201, 609.86, 635.429999999999, 657.64, 593.62, 1370, 570.5, 610.1, 761, 770, 596.023370060814, 677.339443868788, 692.972323406659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~, feed_intake_g_d, bw_kg + adg_g_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156, 3, 119, 216, 137, 201, 109, 154, 135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 206, 207, 214, 215, 216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, 1, 1, 19, 19, 19, 19, 19, 19, 23, 23, 23, 27, 27, 27, 30, 30, 30, 30, 33, 33, 33, 33, 37, 37, 37, 37, 41, 48, 49, 50, 50, 52, 52, 52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 120, 121, 122, 139, 140, 153, 155, 171, 202, 206, 207, 214, 215</t>
+    <t xml:space="preserve">c(858.58, 949.88, 938.04, 536, 691, 400, 462, 607, 361, 1472, 1433, 1415, 540.5, 788, 665.8, 1040.8, 1053, 890.2, 1030.4, 1339, 1201, 1152, 1201, 609.86, 635.429999999999, 657.64, 593.62, 1370, 570.5, 610.1, 761, 770, 596.023370060814, 677.339443868788, 692.972323406659)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(109, 74, 105, 3, 76, 202, 171, 216, 75, 4, 92, 93, 91, 122, 137, 214, 153, 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 206, 207, 214, 215, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1, 1, 1, 19, 19, 19, 19, 19, 19, 23, 23, 23, 27, 27, 27, 30, 30, 30, 30, 33, 33, 33, 33, 37, 37, 37, 37, 41, 48, 49, 50, 50, 52, 52, 52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 73, 77, 106, 119, 120, 121, 135, 139, 140, 154, 155, 156, 201, 206, 207, 215)</t>
   </si>
   <si>
     <t xml:space="preserve">Sheep - High NDF</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 214, 215, 216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">function () 
-return(NULL), function () 
-X, function () 
-index, function () 
-NULL, function () 
-colnames(X), function (value) 
-attr(X, "colnames") &lt;&lt;- value, function (weights) 
+    <t xml:space="preserve">numeric(0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+return(NULL), get_data = function () 
+X, get_index = function () 
+index, get_vary = function () 
+NULL, get_names = function () 
+colnames(X), set_names = function (value) 
+attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
 {
     weights &lt;- weights[cc]
     xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
@@ -393,7 +393,7 @@
     })
     class(ret) &lt;- c("bl_cwlin", "bl")
     return(ret)
-}, function (y) 
+})), basemodel = list(list(fit = function (y) 
 {
     if (!is.null(index)) 
         y &lt;- y[cc]
@@ -406,7 +406,7 @@
     })
     class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
     return(ret)
-}, function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     aggregate &lt;- match.arg(aggregate)
     cf &lt;- switch(aggregate, sum = {
@@ -438,17 +438,19 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, (Intercept), bw_kg, adg_g_day, NDF_nutrition, function () 
+}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     return(MPinvS/sxtx)
-}, function () 
+}, hatvalues = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-}, 844.848146781036, 13.731853218964, 105.031853218964, 93.191853218964, -308.848146781036, -153.848146781036, -444.848146781036, -382.848146781036, -237.848146781036, -483.848146781036, 627.151853218964, 588.151853218964, 570.151853218964, -304.348146781036, -56.848146781036, -179.048146781036, 195.951853218964, 208.151853218964, 45.351853218964, 185.551853218964, 494.151853218964, 356.151853218964, 307.151853218964, 356.151853218964, -234.988146781036, -209.418146781037, -187.208146781036, -251.228146781036, 525.151853218964, -274.348146781036, -234.748146781036, -83.848146781036, -74.848146781036, -248.824776720222, -167.508702912248, -151.875823374377, 4999, 0.1, inbag, FALSE, TRUE, FALSE, new("boost_family_glm", fW = function (f) 
+})), offset = 844.848146781036, ustart = c(`21` = 13.731853218964, `22` = 105.031853218964, `23` = 93.191853218964, `853` = -308.848146781036, `854` = -153.848146781036, `855` = -444.848146781036, `856` = -382.848146781036, `857` = -237.848146781036, `858` = -483.848146781036, `1271` = 627.151853218964, `1272` = 588.151853218964, `1273` = 570.151853218964, `1374` = -304.348146781036, `1375` = -56.848146781036, `1378` = -179.048146781036, `1492` = 195.951853218964, `1493` = 208.151853218964, `1494` = 45.351853218964, 
+`1495` = 185.551853218964, `1586` = 494.151853218964, `1588` = 356.151853218964, `1590` = 307.151853218964, `1591` = 356.151853218964, `1732` = -234.988146781036, `1733` = -209.418146781037, `1734` = -187.208146781036, `1735` = -251.228146781036, `1778` = 525.151853218964, `1952` = -274.348146781036, `1967` = -234.748146781036, `1982` = -83.848146781036, `1983` = -74.848146781036, `1991` = -248.824776720222, `1992` = -167.508702912248, `1993` = -151.875823374377), control = list(mstop = 1200, nu = 0.1, 
+    risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
 sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
@@ -463,8 +465,10 @@
 }, nuisance = function () 
 return(NA), response = function (f) 
 f, rclass = function (f) 
-NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), 858.58, 949.88, 938.04, 536, 691, 400, 462, 607, 361, 1472, 1433, 1415, 540.5, 788, 665.8, 1040.8, 1053, 890.2, 1030.4, 1339, 1201, 1152, 1201, 609.86, 635.429999999999, 657.64, 593.62, 1370, 570.5, 610.1, 761, 770, 596.023370060814, 677.339443868788, 692.972323406659, 21, 22, 23, 853, 854, 855, 856, 857, 858, 1271, 1272, 1273, 1374, 1375, 1378, 1492, 1493, 1494, 1495, 1586, 1588, 1590, 1591, 1732, 1733, 1734, 1735, 1778, 1952, 1967, 1982, 1983, 1991, 1992, 1993, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, function () 
-nuisance, function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
+NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`21` = 858.58, `22` = 949.88, `23` = 938.04, `853` = 536, `854` = 691, `855` = 400, `856` = 462, `857` = 607, `858` = 361, `1271` = 1472, `1272` = 1433, `1273` = 1415, `1374` = 540.5, `1375` = 788, `1378` = 665.8, `1492` = 1040.8, `1493` = 1053, `1494` = 890.2, `1495` = 1030.4, `1586` = 1339, `1588` = 1201, `1590` = 1152, `1591` = 1201, `1732` = 609.86, `1733` = 635.429999999999, `1734` = 657.64, `1735` = 593.62, `1778` = 1370, 
+`1952` = 570.5, `1967` = 610.1, `1982` = 761, `1983` = 770, `1991` = 596.023370060814, `1992` = 677.339443868788, `1993` = 692.972323406659), rownames = c("21", "22", "23", "853", "854", "855", "856", "857", "858", "1271", "1272", "1273", "1374", "1375", "1378", "1492", "1493", "1494", "1495", "1586", "1588", "1590", "1591", "1732", "1733", "1734", "1735", "1778", "1952", "1967", "1982", "1983", "1991", "1992", "1993"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
     res$newX &lt;- newX
@@ -485,19 +489,19 @@
     }
     class(res) &lt;- c("glmboost", "mboost")
     res
-}, function () 
-mstop, function () 
+}, mstop = function () 
+mstop, xselect = function () 
 {
     if (mstop == 0) 
         return(NULL)
     return(xselect[1:mstop])
-}, function () 
-as.vector(fit), function () 
-u, function () 
+}, fitted = function () 
+as.vector(fit), resid = function () 
+u, risk = function () 
 {
     mrisk[1:(mstop + 1)]
-}, function () 
--mrisk[mstop + 1], function (which = NULL, usedonly = FALSE) 
+}, logLik = function () 
+-mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
 {
     if (is.null(which)) 
         which &lt;- 1:length(bnames)
@@ -515,7 +519,7 @@
     if (usedonly) 
         which &lt;- which[which %in% RET$xselect()]
     return(which)
-}, function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     if (mstop == 0) {
         if (length(offset) == 1) {
@@ -602,12 +606,12 @@
         }
     })
     return(pr)
-}, function (which = NULL) 
+}, model.frame = function (which = NULL) 
 {
     if (!is.null(which)) 
         warning("Argument ", sQuote("which"), " is ignored")
     mf
-}, function (i) 
+}, subset = function (i) 
 {
     if (i &lt;= mstop || i &lt;= length(xselect)) {
         if (i != mstop) {
@@ -624,7 +628,7 @@
         }
         tmp &lt;- boost(i - mstop)
     }
-}, function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     if (!is.null(xselect)) 
         indx &lt;- ((1:length(xselect)) &lt;= mstop)
@@ -679,54 +683,45 @@
     names(ret) &lt;- bnames[which]
     attr(ret, "offset") &lt;- offset
     return(ret)
-}, function () 
+}, hatvalues = function () 
 {
     H &lt;- vector(mode = "list", length = ncol(X))
     MPinv &lt;- ret$basemodel[[1]]$MPinv()
     for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
     H
-}, function (newdata) 
+}, newX = function (newdata) 
 {
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, 0, 1, 2, 3, 0, 0, 0, 0, glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">768.108373727632, 1042.3940495827, 909.727934177098, 571.586935992623, 727.261921348127, 447.725579595581, 501.667698697449, 580.373488956393, 292.699371214238, 1376.98298211044, 1339.60828068155, 1318.27609632072, 525.279713128117, 696.857734862653, 700.178650713421, 1098.80166051076, 1154.98441977177, 1016.0091685652, 1062.15336710355, 1318.6798486616, 1221.95136570395, 1212.46893227758, 1223.52192875504, 645.246296744568, 646.555099287143, 658.61912554317, 643.675733693479, 1290.92545727027, 565.649649900018, 582.356057393514, 692.538628760851, 717.075302156521, 578.669334631638, 750.057347241097, 717.453337530551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-90.4716262723681, 92.5140495826951, -28.3120658229016, 35.5869359926235, 36.2619213481269, 47.725579595581, 39.6676986974492, -26.6265110436066, -68.3006287857623, -95.0170178895587, -93.3917193184473, -96.7239036792751, -15.2202868718832, -91.1422651373466, 34.3786507134215, 58.0016605107551, 101.984419771772, 125.809168565195, 31.7533671035512, -20.320151338396, 20.9513657039465, 60.4689322775844, 22.5219287550362, 35.3862967445683, 11.1250992871441, 0.979125543170312, 50.0557336934786, -79.0745427297288, -4.85035009998217, -27.7439426064863, -68.4613712391492, -52.9246978434794, -17.3540354291758, 72.7179033723086, 24.4810141238916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4716262723681, 92.5140495826951, 28.3120658229016, 35.5869359926235, 36.2619213481269, 47.725579595581, 39.6676986974492, 26.6265110436066, 68.3006287857623, 95.0170178895587, 93.3917193184473, 96.7239036792751, 15.2202868718832, 91.1422651373466, 34.3786507134215, 58.0016605107551, 101.984419771772, 125.809168565195, 31.7533671035512, 20.320151338396, 20.9513657039465, 60.4689322775844, 22.5219287550362, 35.3862967445683, 11.1250992871441, 0.979125543170312, 50.0557336934786, 79.0745427297288, 4.85035009998217, 27.7439426064863, 68.4613712391492, 52.9246978434794, 17.3540354291758, 72.7179033723086, 24.4810141238916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140, 202, 139, 155, 2, 91, 121, 76, 92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3, 4, 72, 73, 74, 75, 77, 93, 105, 106, 109, 119, 120, 122, 135, 137, 153, 154, 156, 171, 201, 206, 207, 214, 215, 216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 120, 121, 122, 139, 140, 153, 155, 171, 202, 214, 215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~, feed_intake_g_d, bw_kg.e75 + adg_g_day + NDF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 72, 137, 171, 140, 73, 75, 154, 214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3, 4, 74, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 139, 153, 155, 156, 201, 202, 206, 207, 215, 216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">function () 
-return(NULL), function () 
-X, function () 
-index, function () 
-NULL, function () 
-colnames(X), function (value) 
-attr(X, "colnames") &lt;&lt;- value, function (weights) 
+}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(771.18642949248, 1029.05789777897, 905.893772303916, 556.917883931223, 705.235492558018, 422.32886541523, 467.927343143104, 549.624597109189, 269.863272003028, 1311.43396939196, 1276.68535611739, 1252.58211950403, 459.413336741781, 745.428707441175, 766.494046248527, 1081.83412879453, 1128.0947307396, 999.473415423486, 1051.9956878317, 1337.84267091176, 1241.87995651283, 1228.84762355702, 1238.93812448479, 711.272036129535, 708.820509439499, 728.949896201859, 714.213868157579, 1247.58106045756, 
+620.981704747296, 519.194306496167, 727.604998217493, 758.466784165874, 636.247851160284, 776.469223405769, 728.936307710021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(-87.3935705075197, 79.1778977789703, -32.146227696084, 20.9178839312227, 14.2354925580175, 22.3288654152299, 5.92734314310417, -57.3754028908114, -91.1367279969719, -160.566030608042, -156.314643882611, -162.417880495969, -81.086663258219, -42.5712925588255, 100.694046248527, 41.03412879453, 75.0947307395968, 109.273415423486, 21.5956878317045, -1.15732908824202, 40.8799565128297, 76.8476235570245, 37.9381244847859, 101.412036129535, 73.3905094394996, 71.3098962018589, 120.593868157579, -122.418939542437, 
+50.4817047472961, -90.9056935038328, -33.3950017825073, -11.5332158341264, 40.2244810994702, 99.129779536981, 35.9639843033621)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(87.3935705075197, 79.1778977789703, 32.146227696084, 20.9178839312227, 14.2354925580175, 22.3288654152299, 5.92734314310417, 57.3754028908114, 91.1367279969719, 160.566030608042, 156.314643882611, 162.417880495969, 81.086663258219, 42.5712925588255, 100.694046248527, 41.03412879453, 75.0947307395968, 109.273415423486, 21.5956878317045, 1.15732908824202, 40.8799565128297, 76.8476235570245, 37.9381244847859, 101.412036129535, 73.3905094394996, 71.3098962018589, 120.593868157579, 122.418939542437, 
+50.4817047472961, 90.9056935038328, 33.3950017825073, 11.5332158341264, 40.2244810994702, 99.129779536981, 35.9639843033621)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(77, 135, 120, 215, 207, 72, 121, 106, 201, 206, 119, 139, 73, 155, 140, 154, 156)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2, 3, 4, 74, 75, 76, 91, 92, 93, 105, 109, 122, 137, 153, 171, 202, 214, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+return(NULL), get_data = function () 
+X, get_index = function () 
+index, get_vary = function () 
+NULL, get_names = function () 
+colnames(X), set_names = function (value) 
+attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
 {
     weights &lt;- weights[cc]
     xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
@@ -796,7 +791,7 @@
     })
     class(ret) &lt;- c("bl_cwlin", "bl")
     return(ret)
-}, function (y) 
+})), basemodel = list(list(fit = function (y) 
 {
     if (!is.null(index)) 
         y &lt;- y[cc]
@@ -809,7 +804,7 @@
     })
     class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
     return(ret)
-}, function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     aggregate &lt;- match.arg(aggregate)
     cf &lt;- switch(aggregate, sum = {
@@ -841,17 +836,19 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, (Intercept), bw_kg.e75, adg_g_day, NDF_nutrition, function () 
+}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     return(MPinvS/sxtx)
-}, function () 
+}, hatvalues = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-}, 844.848146781036, 13.731853218964, 105.031853218964, 93.191853218964, -308.848146781036, -153.848146781036, -444.848146781036, -382.848146781036, -237.848146781036, -483.848146781036, 627.151853218964, 588.151853218964, 570.151853218964, -304.348146781036, -56.848146781036, -179.048146781036, 195.951853218964, 208.151853218964, 45.351853218964, 185.551853218964, 494.151853218964, 356.151853218964, 307.151853218964, 356.151853218964, -234.988146781036, -209.418146781037, -187.208146781036, -251.228146781036, 525.151853218964, -274.348146781036, -234.748146781036, -83.848146781036, -74.848146781036, -248.824776720222, -167.508702912248, -151.875823374377, 5000, 0.1, inbag, FALSE, TRUE, FALSE, new("boost_family_glm", fW = function (f) 
+})), offset = 844.848146781036, ustart = c(`21` = 13.731853218964, `22` = 105.031853218964, `23` = 93.191853218964, `853` = -308.848146781036, `854` = -153.848146781036, `855` = -444.848146781036, `856` = -382.848146781036, `857` = -237.848146781036, `858` = -483.848146781036, `1271` = 627.151853218964, `1272` = 588.151853218964, `1273` = 570.151853218964, `1374` = -304.348146781036, `1375` = -56.848146781036, `1378` = -179.048146781036, `1492` = 195.951853218964, `1493` = 208.151853218964, `1494` = 45.351853218964, 
+`1495` = 185.551853218964, `1586` = 494.151853218964, `1588` = 356.151853218964, `1590` = 307.151853218964, `1591` = 356.151853218964, `1732` = -234.988146781036, `1733` = -209.418146781037, `1734` = -187.208146781036, `1735` = -251.228146781036, `1778` = 525.151853218964, `1952` = -274.348146781036, `1967` = -234.748146781036, `1982` = -83.848146781036, `1983` = -74.848146781036, `1991` = -248.824776720222, `1992` = -167.508702912248, `1993` = -151.875823374377), control = list(mstop = 1199, nu = 0.1, 
+    risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
 sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
@@ -866,8 +863,10 @@
 }, nuisance = function () 
 return(NA), response = function (f) 
 f, rclass = function (f) 
-NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), 858.58, 949.88, 938.04, 536, 691, 400, 462, 607, 361, 1472, 1433, 1415, 540.5, 788, 665.8, 1040.8, 1053, 890.2, 1030.4, 1339, 1201, 1152, 1201, 609.86, 635.429999999999, 657.64, 593.62, 1370, 570.5, 610.1, 761, 770, 596.023370060814, 677.339443868788, 692.972323406659, 21, 22, 23, 853, 854, 855, 856, 857, 858, 1271, 1272, 1273, 1374, 1375, 1378, 1492, 1493, 1494, 1495, 1586, 1588, 1590, 1591, 1732, 1733, 1734, 1735, 1778, 1952, 1967, 1982, 1983, 1991, 1992, 1993, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, function () 
-nuisance, function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
+NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`21` = 858.58, `22` = 949.88, `23` = 938.04, `853` = 536, `854` = 691, `855` = 400, `856` = 462, `857` = 607, `858` = 361, `1271` = 1472, `1272` = 1433, `1273` = 1415, `1374` = 540.5, `1375` = 788, `1378` = 665.8, `1492` = 1040.8, `1493` = 1053, `1494` = 890.2, `1495` = 1030.4, `1586` = 1339, `1588` = 1201, `1590` = 1152, `1591` = 1201, `1732` = 609.86, `1733` = 635.429999999999, `1734` = 657.64, `1735` = 593.62, `1778` = 1370, 
+`1952` = 570.5, `1967` = 610.1, `1982` = 761, `1983` = 770, `1991` = 596.023370060814, `1992` = 677.339443868788, `1993` = 692.972323406659), rownames = c("21", "22", "23", "853", "854", "855", "856", "857", "858", "1271", "1272", "1273", "1374", "1375", "1378", "1492", "1493", "1494", "1495", "1586", "1588", "1590", "1591", "1732", "1733", "1734", "1735", "1778", "1952", "1967", "1982", "1983", "1991", "1992", "1993"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
     res$newX &lt;- newX
@@ -888,19 +887,19 @@
     }
     class(res) &lt;- c("glmboost", "mboost")
     res
-}, function () 
-mstop, function () 
+}, mstop = function () 
+mstop, xselect = function () 
 {
     if (mstop == 0) 
         return(NULL)
     return(xselect[1:mstop])
-}, function () 
-as.vector(fit), function () 
-u, function () 
+}, fitted = function () 
+as.vector(fit), resid = function () 
+u, risk = function () 
 {
     mrisk[1:(mstop + 1)]
-}, function () 
--mrisk[mstop + 1], function (which = NULL, usedonly = FALSE) 
+}, logLik = function () 
+-mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
 {
     if (is.null(which)) 
         which &lt;- 1:length(bnames)
@@ -918,7 +917,7 @@
     if (usedonly) 
         which &lt;- which[which %in% RET$xselect()]
     return(which)
-}, function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     if (mstop == 0) {
         if (length(offset) == 1) {
@@ -1005,12 +1004,12 @@
         }
     })
     return(pr)
-}, function (which = NULL) 
+}, model.frame = function (which = NULL) 
 {
     if (!is.null(which)) 
         warning("Argument ", sQuote("which"), " is ignored")
     mf
-}, function (i) 
+}, subset = function (i) 
 {
     if (i &lt;= mstop || i &lt;= length(xselect)) {
         if (i != mstop) {
@@ -1027,7 +1026,7 @@
         }
         tmp &lt;- boost(i - mstop)
     }
-}, function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     if (!is.null(xselect)) 
         indx &lt;- ((1:length(xselect)) &lt;= mstop)
@@ -1082,45 +1081,45 @@
     names(ret) &lt;- bnames[which]
     attr(ret, "offset") &lt;- offset
     return(ret)
-}, function () 
+}, hatvalues = function () 
 {
     H &lt;- vector(mode = "list", length = ncol(X))
     MPinv &lt;- ret$basemodel[[1]]$MPinv()
     for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
     H
-}, function (newdata) 
+}, newX = function (newdata) 
 {
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, 0, 1, 2, 3, 0, 0, 0, 0, glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">768.825747629331, 1041.72706013344, 908.591406808564, 569.913068678887, 725.935413086669, 443.798621170726, 497.170352749686, 576.851816421007, 287.858323500387, 1362.54512511649, 1325.82817890439, 1302.92716887044, 518.396148522191, 704.987833066664, 710.435790574701, 1091.4329431492, 1145.89468010877, 1006.04752260333, 1054.72417539222, 1328.45417750497, 1231.05617350438, 1221.07596497152, 1232.10115656712, 655.065337236304, 655.936156455261, 669.056561746764, 654.020354173555, 1281.2408761995, 573.817333125609, 574.818594484065, 697.577800972247, 722.609069959986, 586.746452502291, 755.748287518542, 721.117552546612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.7542523706693, 91.8470601334385, -29.4485931914362, 33.9130686788872, 34.935413086669, 43.798621170726, 35.1703527496857, -30.1481835789934, -73.1416764996133, -109.454874883509, -107.171821095615, -112.072831129556, -22.1038514778093, -83.0121669333359, 44.6357905747011, 50.6329431491984, 92.8946801087659, 115.847522603331, 24.3241753922159, -10.5458224950278, 30.0561735043761, 69.0759649715239, 31.1011565671247, 45.2053372363036, 20.5061564552616, 11.416561746764, 60.4003541735552, -88.7591238005007, 3.31733312560914, -35.2814055159354, -63.4221990277525, -47.3909300400139, -9.27691755852265, 78.4088436497545, 28.1452291399534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7542523706693, 91.8470601334385, 29.4485931914362, 33.9130686788872, 34.935413086669, 43.798621170726, 35.1703527496857, 30.1481835789934, 73.1416764996133, 109.454874883509, 107.171821095615, 112.072831129556, 22.1038514778093, 83.0121669333359, 44.6357905747011, 50.6329431491984, 92.8946801087659, 115.847522603331, 24.3241753922159, 10.5458224950278, 30.0561735043761, 69.0759649715239, 31.1011565671247, 45.2053372363036, 20.5061564552616, 11.416561746764, 60.4003541735552, 88.7591238005007, 3.31733312560914, 35.2814055159354, 63.4221990277525, 47.3909300400139, 9.27691755852265, 78.4088436497545, 28.1452291399534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92, 105, 216, 202, 156, 74, 201, 3, 93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 4, 72, 73, 75, 76, 77, 91, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 171, 206, 207, 214, 215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3, 4, 74, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 139, 153, 155, 156, 201, 202, 215, 216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">function () 
-return(NULL), function () 
-X, function () 
-index, function () 
-NULL, function () 
-colnames(X), function (value) 
-attr(X, "colnames") &lt;&lt;- value, function (weights) 
+}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(771.52939087784, 1029.40085916433, 906.236733689276, 557.260845316583, 705.578453943378, 422.67182680059, 468.270304528464, 549.967558494549, 270.206233388388, 1311.77693077732, 1277.02831750275, 1252.92508088939, 459.756298127141, 745.771668826535, 766.837007633887, 1082.17709017989, 1128.43769212496, 999.816376808846, 1052.33864921706, 1338.18563229712, 1242.22291789819, 1229.19058494238, 1239.28108587015, 711.614997514895, 709.163470824859, 729.292857587219, 714.556829542939, 1247.92402184292, 
+621.324666132656, 519.537267881527, 727.947959602853, 758.809745551234, 636.590812545644, 776.812184791129, 729.279269095381)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(-87.0506091221596, 79.5208591643303, -31.803266310724, 21.2608453165827, 14.5784539433776, 22.67182680059, 6.27030452846424, -57.0324415054513, -90.7937666116118, -160.223069222682, -155.971682497251, -162.074919110609, -80.7437018728589, -42.2283311734653, 101.037007633887, 41.37709017989, 75.4376921249568, 109.616376808846, 21.9386492170647, -0.814367702882009, 41.2229178981897, 77.1905849423845, 38.2810858701459, 101.754997514895, 73.7334708248598, 71.6528575872189, 120.936829542939, -122.075978157077, 
+50.8246661326561, -90.5627321184727, -33.0520403971473, -11.1902544487663, 40.5674424848303, 99.4727409223411, 36.3069456887222)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(87.0506091221596, 79.5208591643303, 31.803266310724, 21.2608453165827, 14.5784539433776, 22.67182680059, 6.27030452846424, 57.0324415054513, 90.7937666116118, 160.223069222682, 155.971682497251, 162.074919110609, 80.7437018728589, 42.2283311734653, 101.037007633887, 41.37709017989, 75.4376921249568, 109.616376808846, 21.9386492170647, 0.814367702882009, 41.2229178981897, 77.1905849423845, 38.2810858701459, 101.754997514895, 73.7334708248598, 71.6528575872189, 120.936829542939, 122.075978157077, 
+50.8246661326561, 90.5627321184727, 33.0520403971473, 11.1902544487663, 40.5674424848303, 99.4727409223411, 36.3069456887222)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-1-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+return(NULL), get_data = function () 
+X, get_index = function () 
+index, get_vary = function () 
+NULL, get_names = function () 
+colnames(X), set_names = function (value) 
+attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
 {
     weights &lt;- weights[cc]
     xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
@@ -1190,7 +1189,7 @@
     })
     class(ret) &lt;- c("bl_cwlin", "bl")
     return(ret)
-}, function (y) 
+})), basemodel = list(list(fit = function (y) 
 {
     if (!is.null(index)) 
         y &lt;- y[cc]
@@ -1203,7 +1202,7 @@
     })
     class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
     return(ret)
-}, function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     aggregate &lt;- match.arg(aggregate)
     cf &lt;- switch(aggregate, sum = {
@@ -1235,24 +1234,24 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, (Intercept), bw_kg.e75, adg_g_day, NDF_nutrition, function () 
+}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     return(MPinvS/sxtx)
-}, function () 
+}, hatvalues = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-}, 844.848146781036, 13.731853218964, 105.031853218964, 93.191853218964, -308.848146781036, -153.848146781036, -444.848146781036, -382.848146781036, -237.848146781036, -483.848146781036, 627.151853218964, 588.151853218964, 570.151853218964, -304.348146781036, -56.848146781036, -179.048146781036, 195.951853218964, 208.151853218964, 45.351853218964, 185.551853218964, 494.151853218964, 356.151853218964, 307.151853218964, 356.151853218964, -234.988146781036, -209.418146781037, -187.208146781036, -251.228146781036, 525.151853218964, -274.348146781036, -234.748146781036, -83.848146781036, -74.848146781036, -248.824776720222, -167.508702912248, -151.875823374377, 4999, 0.1, inbag, FALSE, TRUE, FALSE, new("boost_family_glm", fW = function (f) 
-return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
-y - f, risk = function (y, f, w = 1) 
-sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
-UseMethod("weighted.mean"), check_y = function (y) 
+})), offset = 760.999987499203, ustart = c(`21` = 1, `22` = 1, `23` = 1, `853` = -1, `854` = -1, `855` = -1, `856` = -1, `857` = -1, `858` = -1, `1271` = 1, `1272` = 1, `1273` = 1, `1374` = -1, `1375` = 1, `1378` = -1, `1492` = 1, `1493` = 1, `1494` = 1, `1495` = 1, `1586` = 1, `1588` = 1, `1590` = 1, `1591` = 1, `1732` = -1, `1733` = -1, `1734` = -1, `1735` = -1, `1778` = 1, `1952` = -1, `1967` = -1, `1982` = 1, `1983` = 1, `1991` = -1, `1992` = -1, `1993` = -1), control = list(mstop = 1200, nu = 0.1, 
+    risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family", ngradient = function (y, f, w = 1) 
+sign(y - f), risk = function (y, f, w = 1) 
+sum(w * loss(y, f), na.rm = TRUE), offset = function (y, w) 
+optimize(risk, interval = range(y), y = y, w = w)$minimum, check_y = function (y) 
 {
     if (!is.numeric(y) || !is.null(dim(y))) 
-        stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
+        stop("response is not a numeric vector but ", sQuote("family = Laplace()"))
     y
 }, weights = function (w) 
 {
@@ -1260,8 +1259,10 @@
 }, nuisance = function () 
 return(NA), response = function (f) 
 f, rclass = function (f) 
-NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), 858.58, 949.88, 938.04, 536, 691, 400, 462, 607, 361, 1472, 1433, 1415, 540.5, 788, 665.8, 1040.8, 1053, 890.2, 1030.4, 1339, 1201, 1152, 1201, 609.86, 635.429999999999, 657.64, 593.62, 1370, 570.5, 610.1, 761, 770, 596.023370060814, 677.339443868788, 692.972323406659, 21, 22, 23, 853, 854, 855, 856, 857, 858, 1271, 1272, 1273, 1374, 1375, 1378, 1492, 1493, 1494, 1495, 1586, 1588, 1590, 1591, 1732, 1733, 1734, 1735, 1778, 1952, 1967, 1982, 1983, 1991, 1992, 1993, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, function () 
-nuisance, function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
+NA, name = "Absolute Error", charloss = "abs(y - f) \n"), response = c(`21` = 858.58, `22` = 949.88, `23` = 938.04, `853` = 536, `854` = 691, `855` = 400, `856` = 462, `857` = 607, `858` = 361, `1271` = 1472, `1272` = 1433, `1273` = 1415, `1374` = 540.5, `1375` = 788, `1378` = 665.8, `1492` = 1040.8, `1493` = 1053, `1494` = 890.2, `1495` = 1030.4, `1586` = 1339, `1588` = 1201, `1590` = 1152, `1591` = 1201, `1732` = 609.86, `1733` = 635.429999999999, `1734` = 657.64, `1735` = 593.62, `1778` = 1370, 
+`1952` = 570.5, `1967` = 610.1, `1982` = 761, `1983` = 770, `1991` = 596.023370060814, `1992` = 677.339443868788, `1993` = 692.972323406659), rownames = c("21", "22", "23", "853", "854", "855", "856", "857", "858", "1271", "1272", "1273", "1374", "1375", "1378", "1492", "1493", "1494", "1495", "1586", "1588", "1590", "1591", "1732", "1733", "1734", "1735", "1778", "1952", "1967", "1982", "1983", "1991", "1992", "1993"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
     res$newX &lt;- newX
@@ -1282,19 +1283,19 @@
     }
     class(res) &lt;- c("glmboost", "mboost")
     res
-}, function () 
-mstop, function () 
+}, mstop = function () 
+mstop, xselect = function () 
 {
     if (mstop == 0) 
         return(NULL)
     return(xselect[1:mstop])
-}, function () 
-as.vector(fit), function () 
-u, function () 
+}, fitted = function () 
+as.vector(fit), resid = function () 
+u, risk = function () 
 {
     mrisk[1:(mstop + 1)]
-}, function () 
--mrisk[mstop + 1], function (which = NULL, usedonly = FALSE) 
+}, logLik = function () 
+-mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
 {
     if (is.null(which)) 
         which &lt;- 1:length(bnames)
@@ -1312,7 +1313,7 @@
     if (usedonly) 
         which &lt;- which[which %in% RET$xselect()]
     return(which)
-}, function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     if (mstop == 0) {
         if (length(offset) == 1) {
@@ -1399,12 +1400,12 @@
         }
     })
     return(pr)
-}, function (which = NULL) 
+}, model.frame = function (which = NULL) 
 {
     if (!is.null(which)) 
         warning("Argument ", sQuote("which"), " is ignored")
     mf
-}, function (i) 
+}, subset = function (i) 
 {
     if (i &lt;= mstop || i &lt;= length(xselect)) {
         if (i != mstop) {
@@ -1421,7 +1422,7 @@
         }
         tmp &lt;- boost(i - mstop)
     }
-}, function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     if (!is.null(xselect)) 
         indx &lt;- ((1:length(xselect)) &lt;= mstop)
@@ -1476,48 +1477,39 @@
     names(ret) &lt;- bnames[which]
     attr(ret, "offset") &lt;- offset
     return(ret)
-}, function () 
+}, hatvalues = function () 
 {
     H &lt;- vector(mode = "list", length = ncol(X))
     MPinv &lt;- ret$basemodel[[1]]$MPinv()
     for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
     H
-}, function (newdata) 
+}, newX = function (newdata) 
 {
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, 0, 1, 2, 3, 0, 0, 0, 0, glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">768.935741561456, 1041.83705406556, 908.701400740689, 570.023062611013, 726.045407018795, 443.908615102852, 497.280346681811, 576.961810353132, 287.968317432512, 1362.65511904862, 1325.93817283651, 1303.03716280257, 518.506142454316, 705.09782699879, 710.545784506827, 1091.54293708132, 1146.00467404089, 1006.15751653546, 1054.83416932434, 1328.5641714371, 1231.1661674365, 1221.18595890365, 1232.21115049925, 655.175331168429, 656.046150387386, 669.16655567889, 654.130348105681, 1281.35087013163, 573.927327057735, 574.92858841619, 697.687794904373, 722.719063892112, 586.856446434417, 755.858281450668, 721.227546478738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-89.6442584385437, 91.957054065564, -29.3385992593106, 34.0230626110126, 35.0454070187945, 43.9086151028516, 35.2803466818113, -30.0381896468679, -73.0316825674878, -109.344880951383, -107.061827163489, -111.96283719743, -21.9938575456836, -82.9021730012103, 44.7457845068267, 50.7429370813238, 93.0046740408916, 115.957516535456, 24.4341693243416, -10.4358285629023, 30.1661674365018, 69.1859589036496, 31.2111504992502, 45.3153311684292, 20.6161503873872, 11.5265556788896, 60.5103481056808, -88.649129868375, 3.42732705773483, -35.1714115838098, -63.312205095627, -47.2809361078884, -9.16692362639697, 78.5188375818801, 28.2552230720789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6442584385437, 91.957054065564, 29.3385992593106, 34.0230626110126, 35.0454070187945, 43.9086151028516, 35.2803466818113, 30.0381896468679, 73.0316825674878, 109.344880951383, 107.061827163489, 111.96283719743, 21.9938575456836, 82.9021730012103, 44.7457845068267, 50.7429370813238, 93.0046740408916, 115.957516535456, 24.4341693243416, 10.4358285629023, 30.1661674365018, 69.1859589036496, 31.2111504992502, 45.3153311684292, 20.6161503873872, 11.5265556788896, 60.5103481056808, 88.649129868375, 3.42732705773483, 35.1714115838098, 63.312205095627, 47.2809361078884, 9.16692362639697, 78.5188375818801, 28.2552230720789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">858.58, 949.88, 938.04, 536, 691, 400, 462, 607, 361, 1472, 1433, 1415, 540.5, 788, 665.8, 1040.8, 1053, 890.2, 1030.4, 1339, 1201, 1152, 1201, 609.86, 635.429999999999, 657.64, 593.62, 1370, 570.5, 610.1, 596.023370060814, 677.339443868788, 692.972323406659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~, feed_intake_g_d, bw_kg.e75 + adg_g_day + NDF_nutrition.sqd + CP_nutrition.log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154, 109, 156, 76, 4, 77, 106, 3, 201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 72, 73, 74, 75, 91, 92, 93, 105, 119, 120, 121, 122, 135, 137, 139, 140, 153, 155, 171, 202, 214, 215, 216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">function () 
-return(NULL), function () 
-X, function () 
-index, function () 
-NULL, function () 
-colnames(X), function (value) 
-attr(X, "colnames") &lt;&lt;- value, function (weights) 
+}, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + bw_kg.sqd + adg_g_day + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(154, 139, 106, 72, 77, 135, 153, 2, 91, 155, 137, 201, 75, 207, 119, 73, 76, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(3, 4, 74, 92, 93, 105, 109, 120, 121, 122, 140, 156, 171, 202, 206, 214, 215)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+return(NULL), get_data = function () 
+X, get_index = function () 
+index, get_vary = function () 
+NULL, get_names = function () 
+colnames(X), set_names = function (value) 
+attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
 {
     weights &lt;- weights[cc]
     xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
@@ -1587,7 +1579,7 @@
     })
     class(ret) &lt;- c("bl_cwlin", "bl")
     return(ret)
-}, function (y) 
+})), basemodel = list(list(fit = function (y) 
 {
     if (!is.null(index)) 
         y &lt;- y[cc]
@@ -1600,7 +1592,7 @@
     })
     class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
     return(ret)
-}, function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     aggregate &lt;- match.arg(aggregate)
     cf &lt;- switch(aggregate, sum = {
@@ -1632,17 +1624,19 @@
     if (!is.null(index)) 
         return(X[index, , drop = FALSE] %*% cf)
     return(X %*% cf)
-}, (Intercept), bw_kg.e75, adg_g_day, NDF_nutrition.sqd, CP_nutrition.log, function () 
+}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     return(MPinvS/sxtx)
-}, function () 
+}, hatvalues = function () 
 {
     if (is.null(MPinvS)) 
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
-}, 849.657125373826, 8.92287462617401, 100.222874626174, 88.3828746261739, -313.657125373826, -158.657125373826, -449.657125373826, -387.657125373826, -242.657125373826, -488.657125373826, 622.342874626174, 583.342874626174, 565.342874626174, -309.157125373826, -61.657125373826, -183.857125373826, 191.142874626174, 203.342874626174, 40.542874626174, 180.742874626174, 489.342874626174, 351.342874626174, 302.342874626174, 351.342874626174, -239.797125373826, -214.227125373827, -192.017125373826, -256.037125373826, 520.342874626174, -279.157125373826, -239.557125373826, -253.633755313012, -172.317681505038, -156.684801967167, 4999, 0.1, inbag, FALSE, TRUE, FALSE, new("boost_family_glm", fW = function (f) 
+})), offset = 844.848146781036, ustart = c(`21` = 13.731853218964, `22` = 105.031853218964, `23` = 93.191853218964, `853` = -308.848146781036, `854` = -153.848146781036, `855` = -444.848146781036, `856` = -382.848146781036, `857` = -237.848146781036, `858` = -483.848146781036, `1271` = 627.151853218964, `1272` = 588.151853218964, `1273` = 570.151853218964, `1374` = -304.348146781036, `1375` = -56.848146781036, `1378` = -179.048146781036, `1492` = 195.951853218964, `1493` = 208.151853218964, `1494` = 45.351853218964, 
+`1495` = 185.551853218964, `1586` = 494.151853218964, `1588` = 356.151853218964, `1590` = 307.151853218964, `1591` = 356.151853218964, `1732` = -234.988146781036, `1733` = -209.418146781037, `1734` = -187.208146781036, `1735` = -251.228146781036, `1778` = 525.151853218964, `1952` = -274.348146781036, `1967` = -234.748146781036, `1982` = -83.848146781036, `1983` = -74.848146781036, `1991` = -248.824776720222, `1992` = -167.508702912248, `1993` = -151.875823374377), control = list(mstop = 1199, nu = 0.1, 
+    risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
 sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
@@ -1657,8 +1651,10 @@
 }, nuisance = function () 
 return(NA), response = function (f) 
 f, rclass = function (f) 
-NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), 858.58, 949.88, 938.04, 536, 691, 400, 462, 607, 361, 1472, 1433, 1415, 540.5, 788, 665.8, 1040.8, 1053, 890.2, 1030.4, 1339, 1201, 1152, 1201, 609.86, 635.429999999999, 657.64, 593.62, 1370, 570.5, 610.1, 596.023370060814, 677.339443868788, 692.972323406659, 21, 22, 23, 853, 854, 855, 856, 857, 858, 1271, 1272, 1273, 1374, 1375, 1378, 1492, 1493, 1494, 1495, 1586, 1588, 1590, 1591, 1732, 1733, 1734, 1735, 1778, 1952, 1967, 1991, 1992, 1993, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, function () 
-nuisance, function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
+NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`21` = 858.58, `22` = 949.88, `23` = 938.04, `853` = 536, `854` = 691, `855` = 400, `856` = 462, `857` = 607, `858` = 361, `1271` = 1472, `1272` = 1433, `1273` = 1415, `1374` = 540.5, `1375` = 788, `1378` = 665.8, `1492` = 1040.8, `1493` = 1053, `1494` = 890.2, `1495` = 1030.4, `1586` = 1339, `1588` = 1201, `1590` = 1152, `1591` = 1201, `1732` = 609.86, `1733` = 635.429999999999, `1734` = 657.64, `1735` = 593.62, `1778` = 1370, 
+`1952` = 570.5, `1967` = 610.1, `1982` = 761, `1983` = 770, `1991` = 596.023370060814, `1992` = 677.339443868788, `1993` = 692.972323406659), rownames = c("21", "22", "23", "853", "854", "855", "856", "857", "858", "1271", "1272", "1273", "1374", "1375", "1378", "1492", "1493", "1494", "1495", "1586", "1588", "1590", "1591", "1732", "1733", "1734", "1735", "1778", "1952", "1967", "1982", "1983", "1991", "1992", "1993"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
 {
     res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
     res$newX &lt;- newX
@@ -1679,19 +1675,19 @@
     }
     class(res) &lt;- c("glmboost", "mboost")
     res
-}, function () 
-mstop, function () 
+}, mstop = function () 
+mstop, xselect = function () 
 {
     if (mstop == 0) 
         return(NULL)
     return(xselect[1:mstop])
-}, function () 
-as.vector(fit), function () 
-u, function () 
+}, fitted = function () 
+as.vector(fit), resid = function () 
+u, risk = function () 
 {
     mrisk[1:(mstop + 1)]
-}, function () 
--mrisk[mstop + 1], function (which = NULL, usedonly = FALSE) 
+}, logLik = function () 
+-mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
 {
     if (is.null(which)) 
         which &lt;- 1:length(bnames)
@@ -1709,7 +1705,7 @@
     if (usedonly) 
         which &lt;- which[which %in% RET$xselect()]
     return(which)
-}, function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     if (mstop == 0) {
         if (length(offset) == 1) {
@@ -1796,12 +1792,12 @@
         }
     })
     return(pr)
-}, function (which = NULL) 
+}, model.frame = function (which = NULL) 
 {
     if (!is.null(which)) 
         warning("Argument ", sQuote("which"), " is ignored")
     mf
-}, function (i) 
+}, subset = function (i) 
 {
     if (i &lt;= mstop || i &lt;= length(xselect)) {
         if (i != mstop) {
@@ -1818,7 +1814,7 @@
         }
         tmp &lt;- boost(i - mstop)
     }
-}, function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
+}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
 {
     if (!is.null(xselect)) 
         indx &lt;- ((1:length(xselect)) &lt;= mstop)
@@ -1873,33 +1869,806 @@
     names(ret) &lt;- bnames[which]
     attr(ret, "offset") &lt;- offset
     return(ret)
-}, function () 
+}, hatvalues = function () 
 {
     H &lt;- vector(mode = "list", length = ncol(X))
     MPinv &lt;- ret$basemodel[[1]]$MPinv()
     for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
     H
-}, function (newdata) 
+}, newX = function (newdata) 
 {
     mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
     X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
     scale(X, center = cm, scale = FALSE)
-}, 0, 1, 2, 3, 4, 0, 0, 0, 0, 0, glmboost.formula(formula = form, data = data, family = Gaussian(), center = FALSE, control = boost_control(mstop = mstop, nu = nu))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">773.327028300256, 1048.06425583709, 908.22937044309, 563.345189153215, 716.257166240024, 437.478644764776, 494.341971100228, 571.640776543799, 290.27237068362, 1373.43179820458, 1334.64378985654, 1309.72298785831, 573.711449607535, 677.028263909771, 672.933413987023, 1089.00072117966, 1146.9178963271, 1003.47409212598, 1056.74900844016, 1333.07594561912, 1231.15072265055, 1219.09166328089, 1230.39540237989, 621.51092725446, 623.347894106385, 628.876658972402, 744.142979405263, 1283.5383942735, 559.803078399492, 595.61390960725, 555.068668272858, 721.424985119995, 680.534059360223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-85.2529716997437, 98.1842558370932, -29.8106295569104, 27.3451891532152, 25.2571662400242, 37.4786447647762, 32.3419711002283, -35.3592234562009, -70.7276293163799, -98.5682017954246, -98.3562101434616, -105.277012141688, 33.211449607535, -110.971736090229, 7.13341398702266, 48.2007211796572, 93.917896327097, 113.274092125984, 26.3490084401583, -5.92405438088008, 30.1507226505523, 67.091663280893, 29.3954023798876, 11.6509272544603, -12.082105893614, -28.7633410275981, 150.522979405263, -86.4616057264964, -10.6969216005081, -14.4860903927503, -40.9547017879559, 44.0855412512074, -12.438264046436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2529716997437, 98.1842558370932, 29.8106295569104, 27.3451891532152, 25.2571662400242, 37.4786447647762, 32.3419711002283, 35.3592234562009, 70.7276293163799, 98.5682017954246, 98.3562101434616, 105.277012141688, 33.211449607535, 110.971736090229, 7.13341398702266, 48.2007211796572, 93.917896327097, 113.274092125984, 26.3490084401583, 5.92405438088008, 30.1507226505523, 67.091663280893, 29.3954023798876, 11.6509272544603, 12.082105893614, 28.7633410275981, 150.522979405263, 86.4616057264964, 10.6969216005081, 14.4860903927503, 40.9547017879559, 44.0855412512074, 12.438264046436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139, 137, 153, 155, 214, 121, 140, 72, 135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 3, 4, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 122, 154, 156, 171, 201, 202, 215, 216</t>
+}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(767.362615839778, 1024.92202820666, 904.499189278393, 560.394885863993, 705.985379704046, 432.140554012107, 478.249460224195, 556.882252096785, 283.587843054407, 1351.69906992878, 1314.81556967587, 1296.36096280298, 473.393360169869, 725.562976463039, 742.112960822665, 1104.34992509946, 1155.27023805134, 1032.1323136172, 1076.14751895149, 1306.44766987304, 1213.1353556294, 1201.27335276372, 1211.2807747263, 688.500809411726, 686.955325325814, 704.704333513675, 690.355390314821, 1273.7298414917, 
+602.629380350206, 535.055689469889, 715.555627726278, 745.535946121519, 618.140289261425, 761.206224347912, 718.354584455509)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(-91.2173841602221, 75.0420282066583, -33.5408107216067, 24.3948858639926, 14.9853797040456, 32.1405540121072, 16.249460224195, -50.1177479032151, -77.4121569455934, -120.300930071216, -118.184430324127, -118.63903719702, -67.1066398301313, -62.4370235369609, 76.312960822665, 63.5499250994637, 102.27023805134, 141.932313617199, 45.7475189514892, -32.552330126965, 12.1353556293975, 49.2733527637222, 10.2807747263023, 78.6408094117263, 51.5253253258147, 47.0643335136751, 96.7353903148214, -96.2701585082964, 
+32.129380350206, -75.0443105301109, -45.4443722737217, -24.4640538784811, 22.1169192006108, 83.8667804791241, 25.3822610488498)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(91.2173841602221, 75.0420282066583, 33.5408107216067, 24.3948858639926, 14.9853797040456, 32.1405540121072, 16.249460224195, 50.1177479032151, 77.4121569455934, 120.300930071216, 118.184430324127, 118.63903719702, 67.1066398301313, 62.4370235369609, 76.312960822665, 63.5499250994637, 102.27023805134, 141.932313617199, 45.7475189514892, 32.552330126965, 12.1353556293975, 49.2733527637222, 10.2807747263023, 78.6408094117263, 51.5253253258147, 47.0643335136751, 96.7353903148214, 96.2701585082964, 
+32.129380350206, 75.0443105301109, 45.4443722737217, 24.4640538784811, 22.1169192006108, 83.8667804791241, 25.3822610488498)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(122, 105, 120, 74, 3, 93, 121, 4, 214, 92, 202, 215, 156, 140, 109, 206, 171)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2, 72, 73, 75, 76, 77, 91, 106, 119, 135, 137, 139, 153, 154, 155, 201, 207, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+return(NULL), get_data = function () 
+X, get_index = function () 
+index, get_vary = function () 
+NULL, get_names = function () 
+colnames(X), set_names = function (value) 
+attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
+{
+    weights &lt;- weights[cc]
+    xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
+    xtx[xtx &lt; .Machine$double.eps] &lt;- 1
+    sxtx &lt;- sqrt(xtx)
+    p &lt;- ncol(X)
+    if (is(X, "Matrix")) {
+        MPinvS &lt;- t(X * weights)/sxtx
+        est &lt;- function(y) MPinvS %*% y
+    }
+    else {
+        MPinvS &lt;- NULL
+        storage.mode(X) &lt;- "double"
+        est &lt;- function(y) crossprod(X, y * weights)/sxtx
+    }
+    fit &lt;- function(y) {
+        if (!is.null(index)) 
+            y &lt;- y[cc]
+        mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
+        xselect &lt;- which(as.logical(mmu == amu))[1]
+        coef &lt;- mu[xselect]/sxtx[xselect]
+        ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
+            if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
+            return(coef * X[index, xselect, drop = FALSE])
+        })
+        class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
+        return(ret)
+    }
+    predict &lt;- function(bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) {
+        aggregate &lt;- match.arg(aggregate)
+        cf &lt;- switch(aggregate, sum = {
+            cf &lt;- rep(0, bm[[1]]$model["p"])
+            for (i in 1:length(bm)) {
+                m &lt;- bm[[i]]$model
+                cf[m[2]] &lt;- cf[m[2]] + m[1]
+            }
+            cf
+        }, cumsum = {
+            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+            if (length(bm) &gt; 2) {
+                for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
+            }
+            cf
+        }, none = {
+            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+            if (length(bm) &gt; 2) {
+                for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
+            }
+            cf
+        })
+        if (!is.null(newdata)) {
+            stopifnot(all(class(newdata) == class(X)))
+            stopifnot(all(colnames(newdata) == colnames(X)))
+            X &lt;- newdata
+            return(X %*% cf)
+        }
+        if (!is.null(index)) 
+            return(X[index, , drop = FALSE] %*% cf)
+        return(X %*% cf)
+    }
+    ret &lt;- list(fit = fit, predict = predict, Xnames = colnames(X), MPinv = function() {
+        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
+        return(MPinvS/sxtx)
+    }, hatvalues = function() {
+        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
+        X %*% (MPinvS/sxtx)
+    })
+    class(ret) &lt;- c("bl_cwlin", "bl")
+    return(ret)
+})), basemodel = list(list(fit = function (y) 
+{
+    if (!is.null(index)) 
+        y &lt;- y[cc]
+    mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
+    xselect &lt;- which(as.logical(mmu == amu))[1]
+    coef &lt;- mu[xselect]/sxtx[xselect]
+    ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
+        if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
+        return(coef * X[index, xselect, drop = FALSE])
+    })
+    class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
+    return(ret)
+}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    aggregate &lt;- match.arg(aggregate)
+    cf &lt;- switch(aggregate, sum = {
+        cf &lt;- rep(0, bm[[1]]$model["p"])
+        for (i in 1:length(bm)) {
+            m &lt;- bm[[i]]$model
+            cf[m[2]] &lt;- cf[m[2]] + m[1]
+        }
+        cf
+    }, cumsum = {
+        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+        if (length(bm) &gt; 2) {
+            for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
+        }
+        cf
+    }, none = {
+        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+        if (length(bm) &gt; 2) {
+            for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
+        }
+        cf
+    })
+    if (!is.null(newdata)) {
+        stopifnot(all(class(newdata) == class(X)))
+        stopifnot(all(colnames(newdata) == colnames(X)))
+        X &lt;- newdata
+        return(X %*% cf)
+    }
+    if (!is.null(index)) 
+        return(X[index, , drop = FALSE] %*% cf)
+    return(X %*% cf)
+}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
+{
+    if (is.null(MPinvS)) 
+        MPinvS &lt;&lt;- t(X * weights)/sxtx
+    return(MPinvS/sxtx)
+}, hatvalues = function () 
+{
+    if (is.null(MPinvS)) 
+        MPinvS &lt;&lt;- t(X * weights)/sxtx
+    X %*% (MPinvS/sxtx)
+})), offset = 844.848146781036, ustart = c(`21` = 13.731853218964, `22` = 105.031853218964, `23` = 93.191853218964, `853` = -308.848146781036, `854` = -153.848146781036, `855` = -444.848146781036, `856` = -382.848146781036, `857` = -237.848146781036, `858` = -483.848146781036, `1271` = 627.151853218964, `1272` = 588.151853218964, `1273` = 570.151853218964, `1374` = -304.348146781036, `1375` = -56.848146781036, `1378` = -179.048146781036, `1492` = 195.951853218964, `1493` = 208.151853218964, `1494` = 45.351853218964, 
+`1495` = 185.551853218964, `1586` = 494.151853218964, `1588` = 356.151853218964, `1590` = 307.151853218964, `1591` = 356.151853218964, `1732` = -234.988146781036, `1733` = -209.418146781037, `1734` = -187.208146781036, `1735` = -251.228146781036, `1778` = 525.151853218964, `1952` = -274.348146781036, `1967` = -234.748146781036, `1982` = -83.848146781036, `1983` = -74.848146781036, `1991` = -248.824776720222, `1992` = -167.508702912248, `1993` = -151.875823374377), control = list(mstop = 1200, nu = 0.1, 
+    risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
+return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
+y - f, risk = function (y, f, w = 1) 
+sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
+UseMethod("weighted.mean"), check_y = function (y) 
+{
+    if (!is.numeric(y) || !is.null(dim(y))) 
+        stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
+    y
+}, weights = function (w) 
+{
+    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
+}, nuisance = function () 
+return(NA), response = function (f) 
+f, rclass = function (f) 
+NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`21` = 858.58, `22` = 949.88, `23` = 938.04, `853` = 536, `854` = 691, `855` = 400, `856` = 462, `857` = 607, `858` = 361, `1271` = 1472, `1272` = 1433, `1273` = 1415, `1374` = 540.5, `1375` = 788, `1378` = 665.8, `1492` = 1040.8, `1493` = 1053, `1494` = 890.2, `1495` = 1030.4, `1586` = 1339, `1588` = 1201, `1590` = 1152, `1591` = 1201, `1732` = 609.86, `1733` = 635.429999999999, `1734` = 657.64, `1735` = 593.62, `1778` = 1370, 
+`1952` = 570.5, `1967` = 610.1, `1982` = 761, `1983` = 770, `1991` = 596.023370060814, `1992` = 677.339443868788, `1993` = 692.972323406659), rownames = c("21", "22", "23", "853", "854", "855", "856", "857", "858", "1271", "1272", "1273", "1374", "1375", "1378", "1492", "1493", "1494", "1495", "1586", "1588", "1590", "1591", "1732", "1733", "1734", "1735", "1778", "1952", "1967", "1982", "1983", "1991", "1992", "1993"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
+{
+    res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
+    res$newX &lt;- newX
+    res$assign &lt;- assign
+    res$center &lt;- cm
+    res$call &lt;- cl
+    res$hatvalues &lt;- function() {
+        H &lt;- vector(mode = "list", length = ncol(X))
+        MPinv &lt;- res$basemodel[[1]]$MPinv()
+        for (j in unique(res$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
+        H
+    }
+    res$rownames &lt;- rownames(mf)
+    res$model.frame &lt;- function(which = NULL) {
+        if (!is.null(which)) 
+            warning("Argument ", sQuote("which"), " is ignored")
+        mf
+    }
+    class(res) &lt;- c("glmboost", "mboost")
+    res
+}, mstop = function () 
+mstop, xselect = function () 
+{
+    if (mstop == 0) 
+        return(NULL)
+    return(xselect[1:mstop])
+}, fitted = function () 
+as.vector(fit), resid = function () 
+u, risk = function () 
+{
+    mrisk[1:(mstop + 1)]
+}, logLik = function () 
+-mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
+{
+    if (is.null(which)) 
+        which &lt;- 1:length(bnames)
+    if (is.character(which)) {
+        i &lt;- sapply(which, function(w) {
+            wi &lt;- grep(w, bnames, fixed = TRUE)
+            if (length(wi) &gt; 0) 
+                return(wi)
+            return(NA)
+        })
+        if (any(is.na(i))) 
+            warning(paste(which[is.na(i)], collapse = ","), " not found")
+        which &lt;- i
+    }
+    if (usedonly) 
+        which &lt;- which[which %in% RET$xselect()]
+    return(which)
+}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    if (mstop == 0) {
+        if (length(offset) == 1) {
+            if (!is.null(newdata)) 
+                return(rep(offset, NROW(newdata)))
+            return(rep(offset, NROW(y)))
+        }
+        if (!is.null(newdata)) {
+            warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
+            return(rep(0, NCOL(newdata)))
+        }
+        return(offset)
+    }
+    if (!is.null(xselect)) 
+        indx &lt;- ((1:length(xselect)) &lt;= mstop)
+    which &lt;- thiswhich(which, usedonly = nw &lt;- is.null(which))
+    if (length(which) == 0) 
+        return(NULL)
+    aggregate &lt;- match.arg(aggregate)
+    pfun &lt;- function(w, agg) {
+        ix &lt;- xselect == w &amp; indx
+        if (!any(ix)) 
+            return(0)
+        if (cwlin) 
+            w &lt;- 1
+        ret &lt;- nu * bl[[w]]$predict(ens[ix], newdata = newdata, aggregate = agg)
+        if (agg == "sum") 
+            return(ret)
+        m &lt;- Matrix(0, nrow = nrow(ret), ncol = sum(indx))
+        m[, which(ix)] &lt;- ret
+        m
+    }
+    pr &lt;- switch(aggregate, sum = {
+        pr &lt;- lapply(which, pfun, agg = "sum")
+        if (!nw) {
+            if (NCOL(pr[[1]]) == 1) {
+                pr &lt;- do.call("cbind", pr)
+                colnames(pr) &lt;- bnames[which]
+                attr(pr, "offset") &lt;- offset
+            }
+            return(pr)
+        } else {
+            ret &lt;- Reduce("+", pr)
+            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
+                warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
+            } else {
+                ret &lt;- ret + offset
+            }
+            return(ret)
+        }
+    }, cumsum = {
+        if (!nw) {
+            pr &lt;- lapply(which, pfun, agg = "none")
+            pr &lt;- lapply(pr, function(x) {
+                .Call("R_mcumsum", as(x, "matrix"), PACKAGE = "mboost")
+            })
+            names(pr) &lt;- bnames[which]
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        } else {
+            pr &lt;- 0
+            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
+            pr &lt;- .Call("R_mcumsum", as(pr, "matrix"), PACKAGE = "mboost")
+            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
+                warning(sQuote("length(offset) &gt; 1"), ": User-specified offset is not a scalar, ", "thus offset not used for prediction when ", sQuote("newdata"), " is specified")
+            } else {
+                pr &lt;- pr + offset
+            }
+            return(pr)
+        }
+    }, none = {
+        if (!nw) {
+            pr &lt;- lapply(which, pfun, agg = "none")
+            for (i in 1:length(pr)) pr[[i]] &lt;- as(pr[[i]], "matrix")
+            names(pr) &lt;- bnames[which]
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        } else {
+            pr &lt;- 0
+            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
+            pr &lt;- as(pr, "matrix")
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        }
+    })
+    return(pr)
+}, model.frame = function (which = NULL) 
+{
+    if (!is.null(which)) 
+        warning("Argument ", sQuote("which"), " is ignored")
+    mf
+}, subset = function (i) 
+{
+    if (i &lt;= mstop || i &lt;= length(xselect)) {
+        if (i != mstop) {
+            mstop &lt;&lt;- i
+            fit &lt;&lt;- RET$predict()
+            u &lt;&lt;- ngradient(y, fit, weights)
+        }
+    }
+    else {
+        if (mstop != length(xselect)) {
+            mstop &lt;&lt;- length(xselect)
+            fit &lt;&lt;- RET$predict()
+            u &lt;&lt;- ngradient(y, fit, weights)
+        }
+        tmp &lt;- boost(i - mstop)
+    }
+}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    if (!is.null(xselect)) 
+        indx &lt;- ((1:length(xselect)) &lt;= mstop)
+    which &lt;- thiswhich(which, usedonly = is.null(which))
+    if (length(which) == 0) 
+        return(NULL)
+    aggregate &lt;- match.arg(aggregate)
+    cfun &lt;- function(w) {
+        ix &lt;- (xselect == w &amp; indx)
+        cf &lt;- numeric(mstop)
+        if (!any(ix)) {
+            if (!cwlin) {
+                nm &lt;- bl[[w]]$Xnames
+                cf &lt;- matrix(0, nrow = length(nm), ncol = mstop)
+            }
+        }
+        else {
+            if (inherits(ens[ix][[1]], "bm_cwlin") &amp;&amp; !cwlin) {
+                cftmp &lt;- sapply(ens[ix], coef, all = TRUE)
+            }
+            else {
+                cftmp &lt;- sapply(ens[ix], coef)
+            }
+            nr &lt;- NROW(cftmp)
+            if (!is.matrix(cftmp)) 
+                nr &lt;- 1
+            cf &lt;- matrix(0, nrow = nr, ncol = mstop)
+            cf[, which(ix)] &lt;- cftmp
+        }
+        if (!is.matrix(cf)) 
+            cf &lt;- matrix(cf, nrow = 1)
+        if (any(sapply(cf, is.null))) {
+            ret &lt;- NULL
+        }
+        else {
+            ret &lt;- switch(aggregate, sum = rowSums(cf) * nu, cumsum = {
+                .Call("R_mcumsum", as(cf, "matrix") * nu, PACKAGE = "mboost")
+            }, none = nu * cf)
+        }
+        if (!cwlin) {
+            nm &lt;- bl[[w]]$Xnames
+            if (is.matrix(ret)) {
+                rownames(ret) &lt;- nm
+            }
+            else {
+                names(ret) &lt;- nm
+            }
+        }
+        ret
+    }
+    ret &lt;- lapply(which, cfun)
+    names(ret) &lt;- bnames[which]
+    attr(ret, "offset") &lt;- offset
+    return(ret)
+}, hatvalues = function () 
+{
+    H &lt;- vector(mode = "list", length = ncol(X))
+    MPinv &lt;- ret$basemodel[[1]]$MPinv()
+    for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
+    H
+}, newX = function (newdata) 
+{
+    mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
+    X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
+    scale(X, center = cm, scale = FALSE)
+}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(767.447368804556, 1024.99219824105, 904.565252704554, 560.645829205284, 706.236323045337, 432.391497353399, 478.500403565487, 557.133195438076, 283.838786395698, 1352.22306488414, 1315.32823534521, 1296.89257940308, 473.592155777536, 725.760371283941, 742.311288951111, 1104.8113579077, 1155.74965876663, 1032.63006617659, 1076.61970323151, 1306.61722395378, 1213.30490971014, 1201.44290684446, 1211.45032880704, 688.69727312628, 687.151789040367, 704.900797228229, 690.551854029375, 1274.20382972149, 
+602.796781385092, 535.311915684076, 715.811853940466, 745.805620273872, 618.34902905187, 761.415923860267, 718.563803831759)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(-91.1326311954444, 75.1121982410465, -33.4747472954462, 24.6458292052841, 15.2363230453371, 32.3914973533987, 16.5004035654865, -49.8668045619236, -77.1612136043019, -119.776935115863, -117.671764654789, -118.107420596916, -66.9078442224636, -62.2396287160594, 76.5112889511113, 64.0113579076976, 102.749658766634, 142.430066176592, 46.2197032315148, -32.3827760462245, 12.304909710138, 49.4429068444629, 10.4503288070428, 78.8372731262799, 51.7217890403682, 47.2607972282286, 96.9318540293749, -95.796170278509, 
+32.2967813850919, -74.7880843159236, -45.1881460595343, -24.194379726128, 22.325658991056, 84.0764799914788, 25.5914804251)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(91.1326311954444, 75.1121982410465, 33.4747472954462, 24.6458292052841, 15.2363230453371, 32.3914973533987, 16.5004035654865, 49.8668045619236, 77.1612136043019, 119.776935115863, 117.671764654789, 118.107420596916, 66.9078442224636, 62.2396287160594, 76.5112889511113, 64.0113579076976, 102.749658766634, 142.430066176592, 46.2197032315148, 32.3827760462245, 12.304909710138, 49.4429068444629, 10.4503288070428, 78.8372731262799, 51.7217890403682, 47.2607972282286, 96.9318540293749, 95.796170278509, 
+32.2967813850919, 74.7880843159236, 45.1881460595343, 24.194379726128, 22.325658991056, 84.0764799914788, 25.5914804251)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+return(NULL), get_data = function () 
+X, get_index = function () 
+index, get_vary = function () 
+NULL, get_names = function () 
+colnames(X), set_names = function (value) 
+attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
+{
+    weights &lt;- weights[cc]
+    xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
+    xtx[xtx &lt; .Machine$double.eps] &lt;- 1
+    sxtx &lt;- sqrt(xtx)
+    p &lt;- ncol(X)
+    if (is(X, "Matrix")) {
+        MPinvS &lt;- t(X * weights)/sxtx
+        est &lt;- function(y) MPinvS %*% y
+    }
+    else {
+        MPinvS &lt;- NULL
+        storage.mode(X) &lt;- "double"
+        est &lt;- function(y) crossprod(X, y * weights)/sxtx
+    }
+    fit &lt;- function(y) {
+        if (!is.null(index)) 
+            y &lt;- y[cc]
+        mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
+        xselect &lt;- which(as.logical(mmu == amu))[1]
+        coef &lt;- mu[xselect]/sxtx[xselect]
+        ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
+            if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
+            return(coef * X[index, xselect, drop = FALSE])
+        })
+        class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
+        return(ret)
+    }
+    predict &lt;- function(bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) {
+        aggregate &lt;- match.arg(aggregate)
+        cf &lt;- switch(aggregate, sum = {
+            cf &lt;- rep(0, bm[[1]]$model["p"])
+            for (i in 1:length(bm)) {
+                m &lt;- bm[[i]]$model
+                cf[m[2]] &lt;- cf[m[2]] + m[1]
+            }
+            cf
+        }, cumsum = {
+            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+            if (length(bm) &gt; 2) {
+                for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
+            }
+            cf
+        }, none = {
+            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+            if (length(bm) &gt; 2) {
+                for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
+            }
+            cf
+        })
+        if (!is.null(newdata)) {
+            stopifnot(all(class(newdata) == class(X)))
+            stopifnot(all(colnames(newdata) == colnames(X)))
+            X &lt;- newdata
+            return(X %*% cf)
+        }
+        if (!is.null(index)) 
+            return(X[index, , drop = FALSE] %*% cf)
+        return(X %*% cf)
+    }
+    ret &lt;- list(fit = fit, predict = predict, Xnames = colnames(X), MPinv = function() {
+        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
+        return(MPinvS/sxtx)
+    }, hatvalues = function() {
+        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
+        X %*% (MPinvS/sxtx)
+    })
+    class(ret) &lt;- c("bl_cwlin", "bl")
+    return(ret)
+})), basemodel = list(list(fit = function (y) 
+{
+    if (!is.null(index)) 
+        y &lt;- y[cc]
+    mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
+    xselect &lt;- which(as.logical(mmu == amu))[1]
+    coef &lt;- mu[xselect]/sxtx[xselect]
+    ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
+        if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
+        return(coef * X[index, xselect, drop = FALSE])
+    })
+    class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
+    return(ret)
+}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    aggregate &lt;- match.arg(aggregate)
+    cf &lt;- switch(aggregate, sum = {
+        cf &lt;- rep(0, bm[[1]]$model["p"])
+        for (i in 1:length(bm)) {
+            m &lt;- bm[[i]]$model
+            cf[m[2]] &lt;- cf[m[2]] + m[1]
+        }
+        cf
+    }, cumsum = {
+        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+        if (length(bm) &gt; 2) {
+            for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
+        }
+        cf
+    }, none = {
+        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+        if (length(bm) &gt; 2) {
+            for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
+        }
+        cf
+    })
+    if (!is.null(newdata)) {
+        stopifnot(all(class(newdata) == class(X)))
+        stopifnot(all(colnames(newdata) == colnames(X)))
+        X &lt;- newdata
+        return(X %*% cf)
+    }
+    if (!is.null(index)) 
+        return(X[index, , drop = FALSE] %*% cf)
+    return(X %*% cf)
+}, Xnames = c("(Intercept)", "bw_kg", "bw_kg.sqd", "adg_g_day", "NDF_nutrition"), MPinv = function () 
+{
+    if (is.null(MPinvS)) 
+        MPinvS &lt;&lt;- t(X * weights)/sxtx
+    return(MPinvS/sxtx)
+}, hatvalues = function () 
+{
+    if (is.null(MPinvS)) 
+        MPinvS &lt;&lt;- t(X * weights)/sxtx
+    X %*% (MPinvS/sxtx)
+})), offset = 760.999987499203, ustart = c(`21` = 1, `22` = 1, `23` = 1, `853` = -1, `854` = -1, `855` = -1, `856` = -1, `857` = -1, `858` = -1, `1271` = 1, `1272` = 1, `1273` = 1, `1374` = -1, `1375` = 1, `1378` = -1, `1492` = 1, `1493` = 1, `1494` = 1, `1495` = 1, `1586` = 1, `1588` = 1, `1590` = 1, `1591` = 1, `1732` = -1, `1733` = -1, `1734` = -1, `1735` = -1, `1778` = 1, `1952` = -1, `1967` = -1, `1982` = 1, `1983` = 1, `1991` = -1, `1992` = -1, `1993` = -1), control = list(mstop = 1200, nu = 0.1, 
+    risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family", ngradient = function (y, f, w = 1) 
+sign(y - f), risk = function (y, f, w = 1) 
+sum(w * loss(y, f), na.rm = TRUE), offset = function (y, w) 
+optimize(risk, interval = range(y), y = y, w = w)$minimum, check_y = function (y) 
+{
+    if (!is.numeric(y) || !is.null(dim(y))) 
+        stop("response is not a numeric vector but ", sQuote("family = Laplace()"))
+    y
+}, weights = function (w) 
+{
+    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
+}, nuisance = function () 
+return(NA), response = function (f) 
+f, rclass = function (f) 
+NA, name = "Absolute Error", charloss = "abs(y - f) \n"), response = c(`21` = 858.58, `22` = 949.88, `23` = 938.04, `853` = 536, `854` = 691, `855` = 400, `856` = 462, `857` = 607, `858` = 361, `1271` = 1472, `1272` = 1433, `1273` = 1415, `1374` = 540.5, `1375` = 788, `1378` = 665.8, `1492` = 1040.8, `1493` = 1053, `1494` = 890.2, `1495` = 1030.4, `1586` = 1339, `1588` = 1201, `1590` = 1152, `1591` = 1201, `1732` = 609.86, `1733` = 635.429999999999, `1734` = 657.64, `1735` = 593.62, `1778` = 1370, 
+`1952` = 570.5, `1967` = 610.1, `1982` = 761, `1983` = 770, `1991` = 596.023370060814, `1992` = 677.339443868788, `1993` = 692.972323406659), rownames = c("21", "22", "23", "853", "854", "855", "856", "857", "858", "1271", "1272", "1273", "1374", "1375", "1378", "1492", "1493", "1494", "1495", "1586", "1588", "1590", "1591", "1732", "1733", "1734", "1735", "1778", "1952", "1967", "1982", "1983", "1991", "1992", "1993"), `(weights)` = c(1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
+{
+    res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
+    res$newX &lt;- newX
+    res$assign &lt;- assign
+    res$center &lt;- cm
+    res$call &lt;- cl
+    res$hatvalues &lt;- function() {
+        H &lt;- vector(mode = "list", length = ncol(X))
+        MPinv &lt;- res$basemodel[[1]]$MPinv()
+        for (j in unique(res$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
+        H
+    }
+    res$rownames &lt;- rownames(mf)
+    res$model.frame &lt;- function(which = NULL) {
+        if (!is.null(which)) 
+            warning("Argument ", sQuote("which"), " is ignored")
+        mf
+    }
+    class(res) &lt;- c("glmboost", "mboost")
+    res
+}, mstop = function () 
+mstop, xselect = function () 
+{
+    if (mstop == 0) 
+        return(NULL)
+    return(xselect[1:mstop])
+}, fitted = function () 
+as.vector(fit), resid = function () 
+u, risk = function () 
+{
+    mrisk[1:(mstop + 1)]
+}, logLik = function () 
+-mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
+{
+    if (is.null(which)) 
+        which &lt;- 1:length(bnames)
+    if (is.character(which)) {
+        i &lt;- sapply(which, function(w) {
+            wi &lt;- grep(w, bnames, fixed = TRUE)
+            if (length(wi) &gt; 0) 
+                return(wi)
+            return(NA)
+        })
+        if (any(is.na(i))) 
+            warning(paste(which[is.na(i)], collapse = ","), " not found")
+        which &lt;- i
+    }
+    if (usedonly) 
+        which &lt;- which[which %in% RET$xselect()]
+    return(which)
+}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    if (mstop == 0) {
+        if (length(offset) == 1) {
+            if (!is.null(newdata)) 
+                return(rep(offset, NROW(newdata)))
+            return(rep(offset, NROW(y)))
+        }
+        if (!is.null(newdata)) {
+            warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
+            return(rep(0, NCOL(newdata)))
+        }
+        return(offset)
+    }
+    if (!is.null(xselect)) 
+        indx &lt;- ((1:length(xselect)) &lt;= mstop)
+    which &lt;- thiswhich(which, usedonly = nw &lt;- is.null(which))
+    if (length(which) == 0) 
+        return(NULL)
+    aggregate &lt;- match.arg(aggregate)
+    pfun &lt;- function(w, agg) {
+        ix &lt;- xselect == w &amp; indx
+        if (!any(ix)) 
+            return(0)
+        if (cwlin) 
+            w &lt;- 1
+        ret &lt;- nu * bl[[w]]$predict(ens[ix], newdata = newdata, aggregate = agg)
+        if (agg == "sum") 
+            return(ret)
+        m &lt;- Matrix(0, nrow = nrow(ret), ncol = sum(indx))
+        m[, which(ix)] &lt;- ret
+        m
+    }
+    pr &lt;- switch(aggregate, sum = {
+        pr &lt;- lapply(which, pfun, agg = "sum")
+        if (!nw) {
+            if (NCOL(pr[[1]]) == 1) {
+                pr &lt;- do.call("cbind", pr)
+                colnames(pr) &lt;- bnames[which]
+                attr(pr, "offset") &lt;- offset
+            }
+            return(pr)
+        } else {
+            ret &lt;- Reduce("+", pr)
+            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
+                warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
+            } else {
+                ret &lt;- ret + offset
+            }
+            return(ret)
+        }
+    }, cumsum = {
+        if (!nw) {
+            pr &lt;- lapply(which, pfun, agg = "none")
+            pr &lt;- lapply(pr, function(x) {
+                .Call("R_mcumsum", as(x, "matrix"), PACKAGE = "mboost")
+            })
+            names(pr) &lt;- bnames[which]
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        } else {
+            pr &lt;- 0
+            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
+            pr &lt;- .Call("R_mcumsum", as(pr, "matrix"), PACKAGE = "mboost")
+            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
+                warning(sQuote("length(offset) &gt; 1"), ": User-specified offset is not a scalar, ", "thus offset not used for prediction when ", sQuote("newdata"), " is specified")
+            } else {
+                pr &lt;- pr + offset
+            }
+            return(pr)
+        }
+    }, none = {
+        if (!nw) {
+            pr &lt;- lapply(which, pfun, agg = "none")
+            for (i in 1:length(pr)) pr[[i]] &lt;- as(pr[[i]], "matrix")
+            names(pr) &lt;- bnames[which]
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        } else {
+            pr &lt;- 0
+            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
+            pr &lt;- as(pr, "matrix")
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        }
+    })
+    return(pr)
+}, model.frame = function (which = NULL) 
+{
+    if (!is.null(which)) 
+        warning("Argument ", sQuote("which"), " is ignored")
+    mf
+}, subset = function (i) 
+{
+    if (i &lt;= mstop || i &lt;= length(xselect)) {
+        if (i != mstop) {
+            mstop &lt;&lt;- i
+            fit &lt;&lt;- RET$predict()
+            u &lt;&lt;- ngradient(y, fit, weights)
+        }
+    }
+    else {
+        if (mstop != length(xselect)) {
+            mstop &lt;&lt;- length(xselect)
+            fit &lt;&lt;- RET$predict()
+            u &lt;&lt;- ngradient(y, fit, weights)
+        }
+        tmp &lt;- boost(i - mstop)
+    }
+}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    if (!is.null(xselect)) 
+        indx &lt;- ((1:length(xselect)) &lt;= mstop)
+    which &lt;- thiswhich(which, usedonly = is.null(which))
+    if (length(which) == 0) 
+        return(NULL)
+    aggregate &lt;- match.arg(aggregate)
+    cfun &lt;- function(w) {
+        ix &lt;- (xselect == w &amp; indx)
+        cf &lt;- numeric(mstop)
+        if (!any(ix)) {
+            if (!cwlin) {
+                nm &lt;- bl[[w]]$Xnames
+                cf &lt;- matrix(0, nrow = length(nm), ncol = mstop)
+            }
+        }
+        else {
+            if (inherits(ens[ix][[1]], "bm_cwlin") &amp;&amp; !cwlin) {
+                cftmp &lt;- sapply(ens[ix], coef, all = TRUE)
+            }
+            else {
+                cftmp &lt;- sapply(ens[ix], coef)
+            }
+            nr &lt;- NROW(cftmp)
+            if (!is.matrix(cftmp)) 
+                nr &lt;- 1
+            cf &lt;- matrix(0, nrow = nr, ncol = mstop)
+            cf[, which(ix)] &lt;- cftmp
+        }
+        if (!is.matrix(cf)) 
+            cf &lt;- matrix(cf, nrow = 1)
+        if (any(sapply(cf, is.null))) {
+            ret &lt;- NULL
+        }
+        else {
+            ret &lt;- switch(aggregate, sum = rowSums(cf) * nu, cumsum = {
+                .Call("R_mcumsum", as(cf, "matrix") * nu, PACKAGE = "mboost")
+            }, none = nu * cf)
+        }
+        if (!cwlin) {
+            nm &lt;- bl[[w]]$Xnames
+            if (is.matrix(ret)) {
+                rownames(ret) &lt;- nm
+            }
+            else {
+                names(ret) &lt;- nm
+            }
+        }
+        ret
+    }
+    ret &lt;- lapply(which, cfun)
+    names(ret) &lt;- bnames[which]
+    attr(ret, "offset") &lt;- offset
+    return(ret)
+}, hatvalues = function () 
+{
+    H &lt;- vector(mode = "list", length = ncol(X))
+    MPinv &lt;- ret$basemodel[[1]]$MPinv()
+    for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
+    H
+}, newX = function (newdata) 
+{
+    mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
+    X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
+    scale(X, center = cm, scale = FALSE)
+}, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
   </si>
 </sst>
 </file>
@@ -2496,559 +3265,554 @@
       <c r="CK1" t="s">
         <v>88</v>
       </c>
+      <c r="CL1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2"/>
-      <c r="B2" t="s">
-        <v>89</v>
+      <c r="B2" t="n">
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>90</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="F2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>4999</v>
-      </c>
       <c r="H2" t="n">
+        <v>198</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.927098702556067</v>
-      </c>
       <c r="J2" t="n">
-        <v>9.61332047805216</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="K2" t="n">
-        <v>0.963403791200689</v>
-      </c>
-      <c r="L2" t="b">
+        <v>15.1027994007799</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.905267120762335</v>
+      </c>
+      <c r="M2" t="b">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>0.941579112882228</v>
-      </c>
       <c r="N2" t="n">
-        <v>8.61655086685785</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="O2" t="n">
-        <v>0.97048840293391</v>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.927098702556067</v>
+        <v>15.1027994007799</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.905267120762335</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>9.61332047805216</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="S2" t="n">
-        <v>0.963403791200689</v>
+        <v>15.1027994007799</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00844025063557081</v>
+        <v>0.905267120762335</v>
       </c>
       <c r="U2" t="n">
-        <v>0.761328035829896</v>
-      </c>
-      <c r="V2"/>
-      <c r="W2" t="n">
-        <v>-691.823918186522</v>
-      </c>
+        <v>0.0639097783265965</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4.48009053153377</v>
+      </c>
+      <c r="W2"/>
       <c r="X2" t="n">
-        <v>15.657929665919</v>
+        <v>-217.41372896161</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.84640919100254</v>
+        <v>13.2087564034637</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.182494379813766</v>
-      </c>
-      <c r="AA2" t="e">
-        <v>#NUM!</v>
+        <v>2.41104835392039</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.33827264174212</v>
       </c>
       <c r="AB2" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0.95333050592565</v>
+      <c r="AC2" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.936819819353675</v>
+        <v>0.741539157747594</v>
       </c>
       <c r="AE2" t="n">
-        <v>6.83210492729153</v>
+        <v>0.666898609430339</v>
       </c>
       <c r="AF2" t="n">
-        <v>6.71555885524479</v>
+        <v>18.2707017959571</v>
       </c>
       <c r="AG2" t="n">
-        <v>-641.450291518558</v>
+        <v>21.3705029573766</v>
       </c>
       <c r="AH2" t="n">
-        <v>14.9633824272698</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.83233847444541</v>
-      </c>
+        <v>-47.4920191796468</v>
+      </c>
+      <c r="AI2"/>
       <c r="AJ2" t="n">
-        <v>0.131219548805815</v>
-      </c>
-      <c r="AK2"/>
+        <v>2.19962856546073</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.381090482735324</v>
+      </c>
       <c r="AL2"/>
-      <c r="AM2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN2"/>
-      <c r="AO2" t="s">
+      <c r="AM2"/>
+      <c r="AN2" t="s">
         <v>93</v>
       </c>
-      <c r="AP2"/>
-      <c r="AQ2" t="s">
+      <c r="AO2"/>
+      <c r="AP2" t="s">
         <v>94</v>
       </c>
-      <c r="AR2"/>
-      <c r="AS2" t="s">
+      <c r="AQ2"/>
+      <c r="AR2" t="s">
         <v>95</v>
       </c>
-      <c r="AT2"/>
-      <c r="AU2" t="s">
-        <v>95</v>
-      </c>
+      <c r="AS2"/>
+      <c r="AT2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU2"/>
       <c r="AV2" t="s">
         <v>96</v>
       </c>
       <c r="AW2" t="s">
         <v>97</v>
       </c>
-      <c r="AX2"/>
-      <c r="AY2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ2" t="s">
+      <c r="AX2" t="s">
         <v>98</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="AY2"/>
+      <c r="AZ2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB2" t="n">
         <v>35</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>99</v>
       </c>
       <c r="BC2" t="s">
         <v>100</v>
       </c>
       <c r="BD2" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-641.450291518558</v>
+        <v>96</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>95</v>
       </c>
       <c r="BF2" t="n">
-        <v>14.9633824272698</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.83233847444541</v>
-      </c>
+        <v>-47.4920191796468</v>
+      </c>
+      <c r="BG2"/>
       <c r="BH2" t="n">
-        <v>0.131219548805815</v>
+        <v>2.19962856546073</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.131219548805815</v>
+        <v>-0.381090482735324</v>
       </c>
       <c r="BJ2" t="n">
-        <v>200.114432094119</v>
-      </c>
-      <c r="BK2" t="s">
+        <v>-0.381090482735324</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>759.421477518517</v>
+      </c>
+      <c r="BL2" t="s">
         <v>101</v>
       </c>
-      <c r="BL2" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>-679.958718916979</v>
+      <c r="BM2" t="s">
+        <v>96</v>
       </c>
       <c r="BN2" t="n">
-        <v>16.5827249040901</v>
+        <v>-341.422197619018</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.76324911936291</v>
+        <v>10.1840833702138</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.130880254257479</v>
-      </c>
-      <c r="BQ2"/>
+        <v>2.52262523194032</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-0.245152669003656</v>
+      </c>
       <c r="BR2"/>
-      <c r="BS2" t="n">
-        <v>841.564723612677</v>
-      </c>
+      <c r="BS2"/>
       <c r="BT2" t="n">
-        <v>161.606004695698</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>102</v>
+        <v>806.913496698164</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>465.491299079146</v>
       </c>
       <c r="BV2" t="s">
         <v>102</v>
       </c>
       <c r="BW2" t="s">
+        <v>102</v>
+      </c>
+      <c r="BX2" t="s">
         <v>103</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BY2" t="s">
         <v>104</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="BZ2" t="n">
         <v>0.155946259824747</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CA2" t="n">
         <v>-0.522514820180757</v>
       </c>
-      <c r="CA2"/>
-      <c r="CB2" t="n">
-        <v>200.114432094119</v>
-      </c>
+      <c r="CB2"/>
       <c r="CC2" t="n">
-        <v>0.977472954850935</v>
-      </c>
-      <c r="CD2"/>
-      <c r="CE2" t="n">
+        <v>759.421477518517</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.870279972052914</v>
+      </c>
+      <c r="CE2"/>
+      <c r="CF2" t="n">
         <v>1</v>
       </c>
-      <c r="CF2" t="n">
-        <v>271.075977558357</v>
-      </c>
       <c r="CG2" t="n">
-        <v>9.59215806039248</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0.115129049242671</v>
-      </c>
+        <v>240.305586515278</v>
+      </c>
+      <c r="CH2"/>
       <c r="CI2" t="n">
-        <v>0.0580326842090571</v>
-      </c>
-      <c r="CJ2"/>
+        <v>0.298992732193698</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.0605535714441245</v>
+      </c>
       <c r="CK2"/>
+      <c r="CL2"/>
     </row>
     <row r="3">
       <c r="A3"/>
-      <c r="B3" t="s">
-        <v>89</v>
+      <c r="B3" t="n">
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>90</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>5000</v>
-      </c>
       <c r="H3" t="n">
+        <v>1199</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.927098702556067</v>
-      </c>
       <c r="J3" t="n">
-        <v>9.61332047805216</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="K3" t="n">
-        <v>0.963403791200689</v>
-      </c>
-      <c r="L3" t="b">
+        <v>15.1027994007799</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.905267120762335</v>
+      </c>
+      <c r="M3" t="b">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
-        <v>0.941579112882228</v>
-      </c>
       <c r="N3" t="n">
-        <v>8.61655086685785</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="O3" t="n">
-        <v>0.97048840293391</v>
-      </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.927098702556067</v>
+        <v>15.1027994007799</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.905267120762335</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>9.61332047805216</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="S3" t="n">
-        <v>0.963403791200689</v>
+        <v>15.1027994007799</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00844025063557081</v>
+        <v>0.905267120762335</v>
       </c>
       <c r="U3" t="n">
-        <v>0.761328035829896</v>
-      </c>
-      <c r="V3"/>
-      <c r="W3" t="n">
-        <v>-691.823918186522</v>
-      </c>
+        <v>0.0639097783265965</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.48009053153377</v>
+      </c>
+      <c r="W3"/>
       <c r="X3" t="n">
-        <v>15.657929665919</v>
+        <v>-217.41372896161</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.84640919100254</v>
+        <v>13.2087564034637</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.182494379813766</v>
-      </c>
-      <c r="AA3" t="e">
-        <v>#NUM!</v>
+        <v>2.41104835392039</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.33827264174212</v>
       </c>
       <c r="AB3" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0.937971062733658</v>
+      <c r="AC3" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.943126110137604</v>
+        <v>0.831921233025325</v>
       </c>
       <c r="AE3" t="n">
-        <v>8.1039109123614</v>
+        <v>0.585976161622329</v>
       </c>
       <c r="AF3" t="n">
-        <v>9.1798548750242</v>
+        <v>11.9348970056027</v>
       </c>
       <c r="AG3" t="n">
-        <v>-574.001892879691</v>
+        <v>12.0329751978119</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.2379234365211</v>
+        <v>-387.335438743573</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.68793890605296</v>
+        <v>13.2087564034637</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0339504367229481</v>
-      </c>
-      <c r="AK3"/>
+        <v>2.62246814238004</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.295454800748915</v>
+      </c>
       <c r="AL3"/>
-      <c r="AM3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN3"/>
-      <c r="AO3" t="s">
+      <c r="AM3"/>
+      <c r="AN3" t="s">
         <v>93</v>
       </c>
-      <c r="AP3"/>
-      <c r="AQ3" t="s">
+      <c r="AO3"/>
+      <c r="AP3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ3"/>
+      <c r="AR3" t="s">
         <v>105</v>
       </c>
-      <c r="AR3"/>
-      <c r="AS3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AT3"/>
-      <c r="AU3" t="s">
-        <v>95</v>
-      </c>
+      <c r="AS3"/>
+      <c r="AT3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU3"/>
       <c r="AV3" t="s">
         <v>96</v>
       </c>
       <c r="AW3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX3" t="s">
         <v>106</v>
       </c>
-      <c r="AX3"/>
-      <c r="AY3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA3" t="n">
+      <c r="AY3"/>
+      <c r="AZ3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB3" t="n">
         <v>35</v>
       </c>
-      <c r="BB3" t="s">
-        <v>99</v>
-      </c>
       <c r="BC3" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>105</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-387.335438743573</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>13.2087564034637</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.62246814238004</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-0.295454800748915</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-0.295454800748915</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>493.339877560175</v>
+      </c>
+      <c r="BL3" t="s">
         <v>107</v>
       </c>
-      <c r="BD3" t="s">
-        <v>105</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-574.001892879691</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>16.2379234365211</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.68793890605296</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0.0339504367229481</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0.0339504367229481</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>221.696766248627</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>101</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>-679.958718916979</v>
+      <c r="BM3" t="s">
+        <v>96</v>
       </c>
       <c r="BN3" t="n">
-        <v>16.5827249040901</v>
+        <v>-341.079236233658</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.76324911936291</v>
+        <v>10.1840833702138</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.130880254257479</v>
-      </c>
-      <c r="BQ3"/>
+        <v>2.52262523194032</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-0.245152669003656</v>
+      </c>
       <c r="BR3"/>
-      <c r="BS3" t="n">
-        <v>795.698659128318</v>
-      </c>
+      <c r="BS3"/>
       <c r="BT3" t="n">
-        <v>115.739940211339</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>102</v>
+        <v>880.675316303749</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>539.59608007009</v>
       </c>
       <c r="BV3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="BW3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="BX3" t="s">
-        <v>104</v>
-      </c>
-      <c r="BY3" t="n">
+        <v>109</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>0.155946259824747</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CA3" t="n">
         <v>-0.522514820180757</v>
       </c>
-      <c r="CA3"/>
-      <c r="CB3" t="n">
-        <v>221.696766248627</v>
-      </c>
+      <c r="CB3"/>
       <c r="CC3" t="n">
-        <v>0.967986666854735</v>
-      </c>
-      <c r="CD3"/>
-      <c r="CE3" t="n">
+        <v>493.339877560175</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.940254269471755</v>
+      </c>
+      <c r="CE3"/>
+      <c r="CF3" t="n">
         <v>1</v>
       </c>
-      <c r="CF3" t="n">
-        <v>271.075977558357</v>
-      </c>
       <c r="CG3" t="n">
-        <v>9.59215806039248</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>0.115129049242671</v>
-      </c>
+        <v>240.305586515278</v>
+      </c>
+      <c r="CH3"/>
       <c r="CI3" t="n">
-        <v>0.0580326842090571</v>
-      </c>
-      <c r="CJ3"/>
+        <v>0.298992732193698</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.0605535714441245</v>
+      </c>
       <c r="CK3"/>
+      <c r="CL3"/>
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" t="s">
-        <v>89</v>
+      <c r="B4" t="n">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>90</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" t="s">
         <v>91</v>
       </c>
-      <c r="F4" t="n">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" t="s">
+        <v>111</v>
+      </c>
       <c r="G4" t="n">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.941579112882228</v>
-      </c>
       <c r="J4" t="n">
-        <v>8.61655086685785</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="K4" t="n">
-        <v>0.97048840293391</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.941579112882228</v>
-      </c>
-      <c r="N4" t="n">
-        <v>8.61655086685785</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.97048840293391</v>
-      </c>
-      <c r="P4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.941579112882228</v>
+        <v>15.1027994007799</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.905267120762335</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4" t="b">
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>8.61655086685785</v>
+        <v>0.427629526497001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.97048840293391</v>
+        <v>23.3208207865901</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0183082077070303</v>
+        <v>0.590281275895245</v>
       </c>
       <c r="U4" t="n">
-        <v>1.23204988452318</v>
-      </c>
-      <c r="V4"/>
-      <c r="W4" t="n">
-        <v>-761.645536460279</v>
-      </c>
-      <c r="X4" t="n">
-        <v>44.2892432494754</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.81013065112311</v>
+        <v>0.427956505470557</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10.7585564710578</v>
+      </c>
+      <c r="W4"/>
+      <c r="X4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y4" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.107243772338607</v>
+        <v>0.421805237959207</v>
       </c>
       <c r="AA4" t="e">
         <v>#NUM!</v>
@@ -3056,238 +3820,199 @@
       <c r="AB4" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0.97452101870536</v>
+      <c r="AC4" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.958200525724631</v>
+        <v>-0.0530085653751178</v>
       </c>
       <c r="AE4" t="n">
-        <v>6.01878315548882</v>
+        <v>-0.156480152936169</v>
       </c>
       <c r="AF4" t="n">
-        <v>5.76670771690976</v>
+        <v>36.8785471671331</v>
       </c>
       <c r="AG4" t="n">
-        <v>-770.330487052947</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>45.1457068246334</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.73447751011189</v>
-      </c>
+        <v>39.8194825936448</v>
+      </c>
+      <c r="AH4"/>
+      <c r="AI4"/>
       <c r="AJ4" t="n">
-        <v>0.126144804077915</v>
+        <v>0.3626840734246</v>
       </c>
       <c r="AK4"/>
       <c r="AL4"/>
-      <c r="AM4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN4"/>
-      <c r="AO4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP4"/>
-      <c r="AQ4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AR4"/>
-      <c r="AS4" t="s">
+      <c r="AM4"/>
+      <c r="AN4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO4"/>
+      <c r="AP4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ4"/>
+      <c r="AR4" t="s">
         <v>95</v>
       </c>
-      <c r="AT4"/>
-      <c r="AU4" t="s">
-        <v>95</v>
-      </c>
+      <c r="AS4"/>
+      <c r="AT4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU4"/>
       <c r="AV4" t="s">
         <v>96</v>
       </c>
       <c r="AW4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AX4"/>
-      <c r="AY4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX4" t="s">
         <v>98</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="AY4"/>
+      <c r="AZ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB4" t="n">
         <v>35</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>99</v>
       </c>
       <c r="BC4" t="s">
         <v>100</v>
       </c>
       <c r="BD4" t="s">
-        <v>109</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-770.330487052947</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>45.1457068246334</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.73447751011189</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF4"/>
+      <c r="BG4"/>
       <c r="BH4" t="n">
-        <v>0.126144804077915</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0.126144804077915</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>76.5407347653395</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>111</v>
+        <v>0.3626840734246</v>
+      </c>
+      <c r="BI4"/>
+      <c r="BJ4"/>
+      <c r="BK4" t="n">
+        <v>761.000005140729</v>
       </c>
       <c r="BL4" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>-723.465843145672</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>42.1821262747411</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>2.75629789890015</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0.0870819218956965</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN4"/>
+      <c r="BO4"/>
+      <c r="BP4"/>
       <c r="BQ4"/>
       <c r="BR4"/>
-      <c r="BS4" t="n">
-        <v>846.871221818286</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>123.405378672614</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>112</v>
-      </c>
+      <c r="BS4"/>
+      <c r="BT4"/>
+      <c r="BU4"/>
       <c r="BV4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BW4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BX4" t="s">
         <v>114</v>
       </c>
-      <c r="BY4" t="n">
-        <v>0.132153700171067</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>-0.522514820180757</v>
-      </c>
+      <c r="BY4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BZ4"/>
       <c r="CA4"/>
-      <c r="CB4" t="n">
-        <v>76.5407347653395</v>
-      </c>
+      <c r="CB4"/>
       <c r="CC4" t="n">
-        <v>0.986387940404869</v>
-      </c>
-      <c r="CD4"/>
-      <c r="CE4" t="n">
+        <v>761.000005140729</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.194335176196954</v>
+      </c>
+      <c r="CE4"/>
+      <c r="CF4" t="n">
         <v>1</v>
       </c>
-      <c r="CF4" t="n">
-        <v>45.1871886172535</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>4.09405582586088</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>0.0217929464680823</v>
-      </c>
+      <c r="CG4"/>
+      <c r="CH4"/>
       <c r="CI4" t="n">
-        <v>0.125775029846937</v>
+        <v>0.0836099527081324</v>
       </c>
       <c r="CJ4"/>
       <c r="CK4"/>
+      <c r="CL4"/>
     </row>
     <row r="5">
       <c r="A5"/>
-      <c r="B5" t="s">
-        <v>89</v>
+      <c r="B5" t="n">
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>90</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4997</v>
-      </c>
       <c r="H5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.941579112882228</v>
-      </c>
       <c r="J5" t="n">
-        <v>8.61655086685785</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="K5" t="n">
-        <v>0.97048840293391</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.941579112882228</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8.61655086685785</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.97048840293391</v>
-      </c>
-      <c r="P5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.941579112882228</v>
+        <v>15.1027994007799</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.905267120762335</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5" t="b">
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>8.61655086685785</v>
+        <v>0.427629526497001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.97048840293391</v>
+        <v>23.3208207865901</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0183082077070303</v>
+        <v>0.590281275895245</v>
       </c>
       <c r="U5" t="n">
-        <v>1.23204988452318</v>
-      </c>
-      <c r="V5"/>
-      <c r="W5" t="n">
-        <v>-761.645536460279</v>
-      </c>
-      <c r="X5" t="n">
-        <v>44.2892432494754</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.81013065112311</v>
+        <v>0.427956505470557</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10.7585564710578</v>
+      </c>
+      <c r="W5"/>
+      <c r="X5" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y5" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.107243772338607</v>
+        <v>0.421805237959207</v>
       </c>
       <c r="AA5" t="e">
         <v>#NUM!</v>
@@ -3295,649 +4020,1022 @@
       <c r="AB5" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0.937022724254568</v>
+      <c r="AC5" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.931919912063377</v>
+        <v>0.190066280590202</v>
       </c>
       <c r="AE5" t="n">
-        <v>11.3087570129533</v>
+        <v>0.0609457601064183</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.1910212340611</v>
+        <v>26.1991371776676</v>
       </c>
       <c r="AG5" t="n">
-        <v>-601.781941746066</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>30.0032974818551</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2.67815803783195</v>
-      </c>
+        <v>18.1219816710696</v>
+      </c>
+      <c r="AH5"/>
+      <c r="AI5"/>
       <c r="AJ5" t="n">
-        <v>0.0463939565331012</v>
+        <v>0.480926402493814</v>
       </c>
       <c r="AK5"/>
       <c r="AL5"/>
-      <c r="AM5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN5"/>
-      <c r="AO5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP5"/>
-      <c r="AQ5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AR5"/>
-      <c r="AS5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AT5"/>
-      <c r="AU5" t="s">
-        <v>95</v>
-      </c>
+      <c r="AM5"/>
+      <c r="AN5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO5"/>
+      <c r="AP5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ5"/>
+      <c r="AR5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS5"/>
+      <c r="AT5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU5"/>
       <c r="AV5" t="s">
         <v>96</v>
       </c>
       <c r="AW5" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX5"/>
-      <c r="AY5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AY5"/>
+      <c r="AZ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB5" t="n">
         <v>35</v>
       </c>
-      <c r="BB5" t="s">
-        <v>99</v>
-      </c>
       <c r="BC5" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="BD5" t="s">
-        <v>115</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-601.781941746066</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>30.0032974818551</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.67815803783195</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>105</v>
+      </c>
+      <c r="BF5"/>
+      <c r="BG5"/>
       <c r="BH5" t="n">
-        <v>0.0463939565331012</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0.0463939565331012</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>258.376243405073</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>118</v>
+        <v>0.480926402493814</v>
+      </c>
+      <c r="BI5"/>
+      <c r="BJ5"/>
+      <c r="BK5" t="n">
+        <v>762.495678727641</v>
       </c>
       <c r="BL5" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>-723.355849213547</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>42.1821262747411</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>2.75629789890015</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0.0870819218956965</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN5"/>
+      <c r="BO5"/>
+      <c r="BP5"/>
       <c r="BQ5"/>
       <c r="BR5"/>
-      <c r="BS5" t="n">
-        <v>860.158185151138</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>136.802335937592</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>119</v>
-      </c>
+      <c r="BS5"/>
+      <c r="BT5"/>
+      <c r="BU5"/>
       <c r="BV5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="BW5" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="BX5" t="s">
-        <v>121</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>0.132153700171067</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>-0.522514820180757</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>114</v>
+      </c>
+      <c r="BZ5"/>
       <c r="CA5"/>
-      <c r="CB5" t="n">
-        <v>258.376243405073</v>
-      </c>
+      <c r="CB5"/>
       <c r="CC5" t="n">
-        <v>0.963153368756983</v>
-      </c>
-      <c r="CD5"/>
-      <c r="CE5" t="n">
+        <v>762.495678727641</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.356255685859358</v>
+      </c>
+      <c r="CE5"/>
+      <c r="CF5" t="n">
         <v>1</v>
       </c>
-      <c r="CF5" t="n">
-        <v>45.1871886172535</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>4.09405582586088</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0.0217929464680823</v>
-      </c>
+      <c r="CG5"/>
+      <c r="CH5"/>
       <c r="CI5" t="n">
-        <v>0.125775029846937</v>
+        <v>0.0836099527081324</v>
       </c>
       <c r="CJ5"/>
       <c r="CK5"/>
+      <c r="CL5"/>
     </row>
     <row r="6">
       <c r="A6"/>
-      <c r="B6" t="s">
-        <v>89</v>
+      <c r="B6" t="n">
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" t="s">
         <v>91</v>
       </c>
-      <c r="F6" t="n">
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>5000</v>
-      </c>
       <c r="H6" t="n">
+        <v>1199</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.939053469278346</v>
-      </c>
       <c r="J6" t="n">
-        <v>8.83291096550856</v>
+        <v>0.595471644366839</v>
       </c>
       <c r="K6" t="n">
-        <v>0.969270876674335</v>
-      </c>
-      <c r="L6" t="b">
+        <v>18.2763177007382</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.71758589937756</v>
+      </c>
+      <c r="M6" t="b">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.941579112882228</v>
-      </c>
       <c r="N6" t="n">
-        <v>8.61655086685785</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="O6" t="n">
-        <v>0.97048840293391</v>
-      </c>
-      <c r="P6" t="b">
+        <v>15.1027994007799</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.905267120762335</v>
+      </c>
+      <c r="Q6" t="b">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.939053469278346</v>
-      </c>
       <c r="R6" t="n">
-        <v>8.83291096550856</v>
+        <v>0.595471644366839</v>
       </c>
       <c r="S6" t="n">
-        <v>0.969270876674335</v>
+        <v>18.2763177007382</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0228797152933467</v>
+        <v>0.71758589937756</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27203936716172</v>
-      </c>
-      <c r="V6"/>
-      <c r="W6" t="n">
-        <v>-430.171964557387</v>
-      </c>
+        <v>0.421558978149646</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11.4486309116802</v>
+      </c>
+      <c r="W6"/>
       <c r="X6" t="n">
-        <v>44.9018424704357</v>
+        <v>-331.714412655353</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.79690343768698</v>
+        <v>0.362918141095703</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.00000623117548620847</v>
+        <v>2.50546814661604</v>
       </c>
       <c r="AA6" t="n">
-        <v>-56.1671796192529</v>
+        <v>-0.158079670339446</v>
       </c>
       <c r="AB6" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AC6" t="n">
-        <v>0.567518016668856</v>
+      <c r="AC6" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0428445415380188</v>
+        <v>0.954262483023902</v>
       </c>
       <c r="AE6" t="n">
-        <v>17.0820713758233</v>
+        <v>0.933336440804194</v>
       </c>
       <c r="AF6" t="n">
-        <v>21.1730683815595</v>
+        <v>7.01428123562007</v>
       </c>
       <c r="AG6" t="n">
-        <v>-83.6724532268275</v>
+        <v>7.90011353072307</v>
       </c>
       <c r="AH6" t="n">
-        <v>37.9260232151426</v>
+        <v>-392.706517364654</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.8726177030106</v>
+        <v>0.369147795562596</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.000146301601264378</v>
+        <v>2.53756808525443</v>
       </c>
       <c r="AK6" t="n">
-        <v>-120.457860274394</v>
+        <v>-0.144097229407333</v>
       </c>
       <c r="AL6"/>
-      <c r="AM6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AN6"/>
-      <c r="AO6" t="s">
-        <v>123</v>
-      </c>
-      <c r="AP6"/>
-      <c r="AQ6" t="s">
-        <v>124</v>
-      </c>
-      <c r="AR6"/>
-      <c r="AS6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AT6"/>
-      <c r="AU6" t="s">
-        <v>95</v>
-      </c>
+      <c r="AM6"/>
+      <c r="AN6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO6"/>
+      <c r="AP6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AQ6"/>
+      <c r="AR6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AS6"/>
+      <c r="AT6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU6"/>
       <c r="AV6" t="s">
         <v>96</v>
       </c>
       <c r="AW6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AX6"/>
-      <c r="AY6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>33</v>
-      </c>
-      <c r="BB6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AY6"/>
+      <c r="AZ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA6" t="s">
         <v>99</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>35</v>
       </c>
       <c r="BC6" t="s">
         <v>100</v>
       </c>
       <c r="BD6" t="s">
-        <v>124</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-83.6724532268275</v>
+        <v>96</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>116</v>
       </c>
       <c r="BF6" t="n">
-        <v>37.9260232151426</v>
+        <v>-392.706517364654</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.8726177030106</v>
+        <v>0.369147795562596</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.000146301601264378</v>
-      </c>
-      <c r="BI6"/>
+        <v>2.53756808525443</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.144097229407333</v>
+      </c>
       <c r="BJ6" t="n">
-        <v>830.053177495517</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>126</v>
+        <v>-0.144097229407333</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>496.993648160616</v>
       </c>
       <c r="BL6" t="s">
-        <v>100</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>-435.08822240882</v>
+        <v>118</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>96</v>
       </c>
       <c r="BN6" t="n">
-        <v>42.198679930569</v>
+        <v>-330.926159094505</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.82593477474864</v>
+        <v>0.362164759887166</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0000424020220869148</v>
+        <v>2.50185549064503</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-54.4168676337618</v>
+        <v>-0.154548408591258</v>
       </c>
       <c r="BR6"/>
-      <c r="BS6" t="n">
-        <v>913.725630722344</v>
-      </c>
+      <c r="BS6"/>
       <c r="BT6" t="n">
-        <v>478.637408313525</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>127</v>
+        <v>889.700165525271</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>558.774006430766</v>
       </c>
       <c r="BV6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="BW6" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="BX6" t="s">
-        <v>129</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.136927028813079</v>
+        <v>120</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>121</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.557179424477729</v>
-      </c>
-      <c r="CA6"/>
-      <c r="CB6" t="n">
-        <v>830.053177495517</v>
-      </c>
+        <v>0.24019329106675</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0.522514820180757</v>
+      </c>
+      <c r="CB6"/>
       <c r="CC6" t="n">
-        <v>0.830653646425539</v>
-      </c>
-      <c r="CD6"/>
-      <c r="CE6" t="n">
+        <v>496.993648160616</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.982560228511391</v>
+      </c>
+      <c r="CE6"/>
+      <c r="CF6" t="n">
         <v>1</v>
       </c>
-      <c r="CF6" t="n">
-        <v>573.681050535614</v>
-      </c>
       <c r="CG6" t="n">
-        <v>4.57806660279743</v>
+        <v>86.2558616775736</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0351387358805917</v>
+        <v>0.00881006183597888</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.000231197757506445</v>
+        <v>0.045396168573766</v>
       </c>
       <c r="CJ6" t="n">
-        <v>81.8774188195378</v>
+        <v>0.0197741576012754</v>
       </c>
       <c r="CK6"/>
+      <c r="CL6"/>
     </row>
     <row r="7">
       <c r="A7"/>
-      <c r="B7" t="s">
-        <v>89</v>
+      <c r="B7" t="n">
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>90</v>
       </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" t="s">
         <v>91</v>
       </c>
-      <c r="F7" t="n">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
+      <c r="F7" t="s">
+        <v>92</v>
+      </c>
       <c r="G7" t="n">
-        <v>5000</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.939053469278346</v>
-      </c>
       <c r="J7" t="n">
-        <v>8.83291096550856</v>
+        <v>0.595471644366839</v>
       </c>
       <c r="K7" t="n">
-        <v>0.969270876674335</v>
-      </c>
-      <c r="L7" t="b">
+        <v>18.2763177007382</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.71758589937756</v>
+      </c>
+      <c r="M7" t="b">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0.941579112882228</v>
-      </c>
       <c r="N7" t="n">
-        <v>8.61655086685785</v>
+        <v>0.78673019538646</v>
       </c>
       <c r="O7" t="n">
-        <v>0.97048840293391</v>
-      </c>
-      <c r="P7" t="b">
+        <v>15.1027994007799</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.905267120762335</v>
+      </c>
+      <c r="Q7" t="b">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0.939053469278346</v>
-      </c>
       <c r="R7" t="n">
-        <v>8.83291096550856</v>
+        <v>0.595471644366839</v>
       </c>
       <c r="S7" t="n">
-        <v>0.969270876674335</v>
+        <v>18.2763177007382</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0228797152933467</v>
+        <v>0.71758589937756</v>
       </c>
       <c r="U7" t="n">
-        <v>1.27203936716172</v>
-      </c>
-      <c r="V7"/>
-      <c r="W7" t="n">
-        <v>-430.171964557387</v>
-      </c>
+        <v>0.421558978149646</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11.4486309116802</v>
+      </c>
+      <c r="W7"/>
       <c r="X7" t="n">
-        <v>44.9018424704357</v>
+        <v>-331.714412655353</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.79690343768698</v>
+        <v>0.362918141095703</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.00000623117548620847</v>
+        <v>2.50546814661604</v>
       </c>
       <c r="AA7" t="n">
-        <v>-56.1671796192529</v>
+        <v>-0.158079670339446</v>
       </c>
       <c r="AB7" t="e">
         <v>#NUM!</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0.958344677619963</v>
+      <c r="AC7" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.970380267508456</v>
+        <v>0.908049277189129</v>
       </c>
       <c r="AE7" t="n">
-        <v>6.71186589520036</v>
+        <v>0.898158002620672</v>
       </c>
       <c r="AF7" t="n">
-        <v>5.14363005827731</v>
+        <v>9.36034182244845</v>
       </c>
       <c r="AG7" t="n">
-        <v>-518.131893889692</v>
+        <v>9.79343143329898</v>
       </c>
       <c r="AH7" t="n">
-        <v>44.8834330093232</v>
+        <v>-270.722307946052</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.94645858335006</v>
+        <v>0.356688486628809</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0000953269698811193</v>
+        <v>2.47336820797764</v>
       </c>
       <c r="AK7" t="n">
-        <v>-41.8776354867644</v>
+        <v>-0.172062111271559</v>
       </c>
       <c r="AL7"/>
-      <c r="AM7" t="s">
+      <c r="AM7"/>
+      <c r="AN7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO7"/>
+      <c r="AP7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AQ7"/>
+      <c r="AR7" t="s">
         <v>122</v>
       </c>
-      <c r="AN7"/>
-      <c r="AO7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AP7"/>
-      <c r="AQ7" t="s">
-        <v>130</v>
-      </c>
-      <c r="AR7"/>
-      <c r="AS7" t="s">
-        <v>100</v>
-      </c>
-      <c r="AT7"/>
-      <c r="AU7" t="s">
-        <v>95</v>
-      </c>
+      <c r="AS7"/>
+      <c r="AT7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU7"/>
       <c r="AV7" t="s">
         <v>96</v>
       </c>
       <c r="AW7" t="s">
-        <v>131</v>
-      </c>
-      <c r="AX7"/>
-      <c r="AY7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>33</v>
-      </c>
-      <c r="BB7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AY7"/>
+      <c r="AZ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA7" t="s">
         <v>99</v>
       </c>
+      <c r="BB7" t="n">
+        <v>35</v>
+      </c>
       <c r="BC7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>117</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-270.722307946052</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.356688486628809</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.47336820797764</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0.172062111271559</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0.172062111271559</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>531.765598909873</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>124</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-330.926159094505</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.36285263396214</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2.50185549064503</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-0.154548408591258</v>
+      </c>
+      <c r="BR7"/>
+      <c r="BS7"/>
+      <c r="BT7" t="n">
+        <v>802.487906855925</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>471.56174776142</v>
+      </c>
+      <c r="BV7" t="s">
         <v>125</v>
       </c>
-      <c r="BD7" t="s">
-        <v>130</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>-518.131893889692</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>44.8834330093232</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.94645858335006</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0.0000953269698811193</v>
-      </c>
-      <c r="BI7"/>
-      <c r="BJ7" t="n">
-        <v>309.199846413452</v>
-      </c>
-      <c r="BK7" t="s">
+      <c r="BW7" t="s">
+        <v>125</v>
+      </c>
+      <c r="BX7" t="s">
         <v>126</v>
       </c>
-      <c r="BL7" t="s">
+      <c r="BY7" t="s">
+        <v>127</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.24019329106675</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0.522514820180757</v>
+      </c>
+      <c r="CB7"/>
+      <c r="CC7" t="n">
+        <v>531.765598909873</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.961830064172989</v>
+      </c>
+      <c r="CE7"/>
+      <c r="CF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>86.2558616775736</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.00881006183597888</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.045396168573766</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.0197741576012754</v>
+      </c>
+      <c r="CK7"/>
+      <c r="CL7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.595471644366839</v>
+      </c>
+      <c r="K8" t="n">
+        <v>18.2763177007382</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.71758589937756</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.378706612171384</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22.6762869574862</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.586110934776298</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.537078298132098</v>
+      </c>
+      <c r="V8" t="n">
+        <v>12.6524441262576</v>
+      </c>
+      <c r="W8"/>
+      <c r="X8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.361832656011473</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.0131613808165207</v>
+      </c>
+      <c r="AB8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AC8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.2333659282884</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.398157375655065</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>36.4244377255071</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>36.179879240172</v>
+      </c>
+      <c r="AH8"/>
+      <c r="AI8"/>
+      <c r="AJ8" t="n">
+        <v>0.309965837333972</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.0131613808165207</v>
+      </c>
+      <c r="AL8"/>
+      <c r="AM8"/>
+      <c r="AN8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO8"/>
+      <c r="AP8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AQ8"/>
+      <c r="AR8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AS8"/>
+      <c r="AT8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU8"/>
+      <c r="AV8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AY8"/>
+      <c r="AZ8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>35</v>
+      </c>
+      <c r="BC8" t="s">
         <v>100</v>
       </c>
-      <c r="BM7" t="n">
-        <v>-435.08822240882</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>42.198679930569</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>2.82593477474864</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.0000424020220869148</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-54.4168676337618</v>
-      </c>
-      <c r="BR7"/>
-      <c r="BS7" t="n">
-        <v>827.331740303144</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>392.243517894324</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>127</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>127</v>
-      </c>
-      <c r="BW7" t="s">
+      <c r="BD8" t="s">
+        <v>96</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>116</v>
+      </c>
+      <c r="BF8"/>
+      <c r="BG8"/>
+      <c r="BH8" t="n">
+        <v>0.309965837333972</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0.0131613808165207</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0.0131613808165207</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>890.199979498374</v>
+      </c>
+      <c r="BL8" t="s">
         <v>128</v>
       </c>
-      <c r="BX7" t="s">
-        <v>129</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0.136927028813079</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>-0.557179424477729</v>
-      </c>
-      <c r="CA7"/>
-      <c r="CB7" t="n">
-        <v>309.199846413452</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>0.98106826285477</v>
-      </c>
-      <c r="CD7"/>
-      <c r="CE7" t="n">
+      <c r="BM8" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN8"/>
+      <c r="BO8"/>
+      <c r="BP8"/>
+      <c r="BQ8"/>
+      <c r="BR8"/>
+      <c r="BS8"/>
+      <c r="BT8"/>
+      <c r="BU8"/>
+      <c r="BV8" t="s">
+        <v>114</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>114</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>114</v>
+      </c>
+      <c r="BZ8"/>
+      <c r="CA8" t="n">
+        <v>-0.522514820180757</v>
+      </c>
+      <c r="CB8"/>
+      <c r="CC8" t="n">
+        <v>890.199979498374</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.192684485738253</v>
+      </c>
+      <c r="CE8"/>
+      <c r="CF8" t="n">
         <v>1</v>
       </c>
-      <c r="CF7" t="n">
-        <v>573.681050535614</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>4.57806660279743</v>
-      </c>
-      <c r="CH7" t="n">
-        <v>0.0351387358805917</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>0.000231197757506445</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>81.8774188195378</v>
-      </c>
-      <c r="CK7"/>
+      <c r="CG8"/>
+      <c r="CH8"/>
+      <c r="CI8" t="n">
+        <v>0.0733507584108677</v>
+      </c>
+      <c r="CJ8"/>
+      <c r="CK8"/>
+      <c r="CL8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.595471644366839</v>
+      </c>
+      <c r="K9" t="n">
+        <v>18.2763177007382</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.71758589937756</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.378706612171384</v>
+      </c>
+      <c r="S9" t="n">
+        <v>22.6762869574862</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.586110934776298</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.537078298132098</v>
+      </c>
+      <c r="V9" t="n">
+        <v>12.6524441262576</v>
+      </c>
+      <c r="W9"/>
+      <c r="X9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.361832656011473</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.0131613808165207</v>
+      </c>
+      <c r="AB9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AC9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.309811040541565</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.364660358022879</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>35.3279517299539</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>35.8495510123463</v>
+      </c>
+      <c r="AH9"/>
+      <c r="AI9"/>
+      <c r="AJ9" t="n">
+        <v>0.413699474688974</v>
+      </c>
+      <c r="AK9"/>
+      <c r="AL9"/>
+      <c r="AM9"/>
+      <c r="AN9" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO9"/>
+      <c r="AP9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AQ9"/>
+      <c r="AR9" t="s">
+        <v>122</v>
+      </c>
+      <c r="AS9"/>
+      <c r="AT9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU9"/>
+      <c r="AV9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>123</v>
+      </c>
+      <c r="AY9"/>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>35</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>117</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF9"/>
+      <c r="BG9"/>
+      <c r="BH9" t="n">
+        <v>0.413699474688974</v>
+      </c>
+      <c r="BI9"/>
+      <c r="BJ9"/>
+      <c r="BK9" t="n">
+        <v>691.561248188406</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>96</v>
+      </c>
+      <c r="BN9"/>
+      <c r="BO9"/>
+      <c r="BP9"/>
+      <c r="BQ9"/>
+      <c r="BR9"/>
+      <c r="BS9"/>
+      <c r="BT9"/>
+      <c r="BU9"/>
+      <c r="BV9" t="s">
+        <v>114</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>114</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>114</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>114</v>
+      </c>
+      <c r="BZ9"/>
+      <c r="CA9"/>
+      <c r="CB9"/>
+      <c r="CC9" t="n">
+        <v>691.561248188406</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.190687596206772</v>
+      </c>
+      <c r="CE9"/>
+      <c r="CF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG9"/>
+      <c r="CH9"/>
+      <c r="CI9" t="n">
+        <v>0.0733507584108677</v>
+      </c>
+      <c r="CJ9"/>
+      <c r="CK9"/>
+      <c r="CL9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Figures.out/gbr_out_sheep_hin.xlsx
+++ b/Figures.out/gbr_out_sheep_hin.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t xml:space="preserve">matrix.NA..nrow...n.rows..ncol...1.</t>
   </si>
@@ -254,6 +254,42 @@
     <t xml:space="preserve">var.corr.bw.ndf</t>
   </si>
   <si>
+    <t xml:space="preserve">var.imp.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.NDF_Digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var.imp.rel.NDF_Digest</t>
+  </si>
+  <si>
     <t xml:space="preserve">coef.NDF_Digest</t>
   </si>
   <si>
@@ -287,6 +323,60 @@
     <t xml:space="preserve">sd.coef.NDF_digest</t>
   </si>
   <si>
+    <t xml:space="preserve">mean.var.imp.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean.var.imp.rel.NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.BW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.ADG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.NDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.CP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sd.var.imp.NDF_digest</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sheep</t>
   </si>
   <si>
@@ -302,7 +392,7 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(3, 137, 214, 139, 154, 2, 206, 93, 91, 72, 135, 77, 171, 140, 73, 75, 74, 76)</t>
+    <t xml:space="preserve">c(91, 202, 3, 135, 215, 120, 206, 76, 137, 122, 121, 201, 156, 214, 140, 72, 74, 153)</t>
   </si>
   <si>
     <t xml:space="preserve">c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 206, 207, 214, 215, 216)</t>
@@ -311,7 +401,7 @@
     <t xml:space="preserve">c(1, 1, 1, 19, 19, 19, 19, 19, 19, 23, 23, 23, 27, 27, 27, 30, 30, 30, 30, 33, 33, 33, 33, 37, 37, 37, 37, 41, 48, 49, 50, 50, 52, 52, 52)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(4, 92, 105, 106, 109, 119, 120, 121, 122, 153, 155, 156, 201, 202, 207, 215, 216)</t>
+    <t xml:space="preserve">c(2, 4, 73, 75, 77, 92, 93, 105, 106, 109, 119, 139, 154, 155, 171, 207, 216)</t>
   </si>
   <si>
     <t xml:space="preserve">Sheep - High NDF</t>
@@ -320,10 +410,10 @@
     <t xml:space="preserve">numeric(0)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 214, 215, 216)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2, 3, 72, 73, 74, 75, 76, 77, 91, 93, 135, 137, 139, 140, 154, 171, 206, 214)</t>
+    <t xml:space="preserve">c(2, 3, 4, 105, 106, 109, 153, 154, 155, 156, 202, 214, 215, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(3, 72, 74, 76, 91, 120, 121, 122, 135, 137, 140, 153, 156, 201, 202, 206, 214, 215)</t>
   </si>
   <si>
     <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
@@ -458,7 +548,7 @@
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
 })), offset = 844.848146781036, ustart = c(`21` = 13.731853218964, `22` = 105.031853218964, `23` = 93.191853218964, `853` = -308.848146781036, `854` = -153.848146781036, `855` = -444.848146781036, `856` = -382.848146781036, `857` = -237.848146781036, `858` = -483.848146781036, `1271` = 627.151853218964, `1272` = 588.151853218964, `1273` = 570.151853218964, `1374` = -304.348146781036, `1375` = -56.848146781036, `1378` = -179.048146781036, `1492` = 195.951853218964, `1493` = 208.151853218964, `1494` = 45.351853218964, 
-`1495` = 185.551853218964, `1586` = 494.151853218964, `1588` = 356.151853218964, `1590` = 307.151853218964, `1591` = 356.151853218964, `1732` = -234.988146781036, `1733` = -209.418146781037, `1734` = -187.208146781036, `1735` = -251.228146781036, `1778` = 525.151853218964, `1952` = -274.348146781036, `1967` = -234.748146781036, `1982` = -83.848146781036, `1983` = -74.848146781036, `1991` = -248.824776720222, `1992` = -167.508702912248, `1993` = -151.875823374377), control = list(mstop = 1100, nu = 0.1, 
+`1495` = 185.551853218964, `1586` = 494.151853218964, `1588` = 356.151853218964, `1590` = 307.151853218964, `1591` = 356.151853218964, `1732` = -234.988146781036, `1733` = -209.418146781037, `1734` = -187.208146781036, `1735` = -251.228146781036, `1778` = 525.151853218964, `1952` = -274.348146781036, `1967` = -234.748146781036, `1982` = -83.848146781036, `1983` = -74.848146781036, `1991` = -248.824776720222, `1992` = -167.508702912248, `1993` = -151.875823374377), control = list(mstop = 1000, nu = 0.1, 
     risk = "inbag", stopintern = FALSE, center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
@@ -706,19 +796,19 @@
 }, assign = 0:3, center = c(0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
   </si>
   <si>
-    <t xml:space="preserve">c(771.302404347456, 1028.06882412503, 905.501339622165, 556.469703362378, 704.275644489561, 421.426503463779, 466.546716545186, 548.333879118102, 269.222881801454, 1307.87926641256, 1273.29086896561, 1249.07357988955, 456.293385567864, 748.108730995909, 770.093968607072, 1080.99302694637, 1126.70364483632, 998.747890096663, 1051.54607696339, 1338.44776496383, 1242.60529532231, 1229.39646001032, 1239.4277714373, 714.900669563718, 712.252732992875, 732.791019024907, 718.078193448729, 1245.21854422282, 
-624.089542208182, 516.223187391362, 729.64443671251, 760.826489704171, 639.505722134694, 777.966612264542, 729.684889076011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(-87.2775956525443, 78.1888241250286, -32.5386603778352, 20.4697033623776, 13.2756444895606, 21.4265034637789, 4.54671654518569, -58.6661208818975, -91.7771181985463, -164.120733587436, -159.709131034386, -165.926420110451, -84.2066144321357, -39.8912690040906, 104.293968607072, 40.1930269463708, 73.7036448363212, 108.547890096663, 21.1460769633945, -0.552235036169805, 41.6052953223075, 77.3964600103232, 38.4277714372956, 105.040669563718, 76.8227329928756, 75.1510190249066, 124.458193448729, -124.78145577718, 
-53.5895422081824, -93.8768126086385, -31.3555632874902, -9.17351029582881, 43.4823520738801, 100.627168395754, 36.7125656693516)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(87.2775956525443, 78.1888241250286, 32.5386603778352, 20.4697033623776, 13.2756444895606, 21.4265034637789, 4.54671654518569, 58.6661208818975, 91.7771181985463, 164.120733587436, 159.709131034386, 165.926420110451, 84.2066144321357, 39.8912690040906, 104.293968607072, 40.1930269463708, 73.7036448363212, 108.547890096663, 21.1460769633945, 0.552235036169805, 41.6052953223075, 77.3964600103232, 38.4277714372956, 105.040669563718, 76.8227329928756, 75.1510190249066, 124.458193448729, 124.78145577718, 
-53.5895422081824, 93.8768126086385, 31.3555632874902, 9.17351029582881, 43.4823520738801, 100.627168395754, 36.7125656693516)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(119, 109, 216, 201, 122, 121, 92, 207, 4, 106, 153, 105, 156, 202, 120, 155, 215)</t>
+    <t xml:space="preserve">c(771.529842758817, 1027.43222656515, 905.373644923977, 555.655432400356, 703.073221611949, 420.018958081447, 464.68944135866, 546.64548033187, 267.942574527385, 1304.29492069688, 1269.84876704823, 1245.47525436678, 452.706139684691, 750.761181189758, 773.711745290515, 1080.04300123485, 1125.21438015318, 997.807297561251, 1050.96139951041, 1339.55813896423, 1243.74979916051, 1230.34709585831, 1240.32690399967, 718.499019602951, 715.646606968918, 736.62462235014, 721.92191476379, 1242.84579917856, 
+627.109807386002, 512.770022792721, 731.543880045214, 763.06815096667, 642.635365686543, 779.41369725953, 730.317391531549)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(-87.0501572411832, 77.5522265651488, -32.6663550760231, 19.6554324003556, 12.0732216119491, 20.0189580814471, 2.68944135865991, -60.3545196681296, -93.0574254726153, -167.705079303121, -163.151232951768, -169.524745633219, -87.793860315309, -37.2388188102423, 107.911745290515, 39.2430012348459, 72.214380153182, 107.607297561251, 20.5613995104131, 0.558138964230693, 42.7497991605071, 78.3470958583061, 39.3269039996676, 108.639019602951, 80.216606968919, 78.9846223501396, 128.30191476379, -127.154200821442, 
+56.6098073860023, -97.3299772072793, -29.4561199547855, -6.93184903332985, 46.6119956257289, 102.074253390742, 37.3450681248895)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(87.0501572411832, 77.5522265651488, 32.6663550760231, 19.6554324003556, 12.0732216119491, 20.0189580814471, 2.68944135865991, 60.3545196681296, 93.0574254726153, 167.705079303121, 163.151232951768, 169.524745633219, 87.793860315309, 37.2388188102423, 107.911745290515, 39.2430012348459, 72.214380153182, 107.607297561251, 20.5613995104131, 0.558138964230693, 42.7497991605071, 78.3470958583061, 39.3269039996676, 108.639019602951, 80.216606968919, 78.9846223501396, 128.30191476379, 127.154200821442, 
+56.6098073860023, 97.3299772072793, 29.4561199547855, 6.93184903332985, 46.6119956257289, 102.074253390742, 37.3450681248895)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(154, 106, 93, 77, 109, 207, 73, 92, 4, 171, 119, 105, 75, 155, 216, 139, 2)</t>
   </si>
   <si>
     <t xml:space="preserve">c(858.58, 949.88, 938.04, 536, 691, 400, 462, 607, 361, 1472, 1433, 1415, 540.5, 788, 665.8, 1040.8, 1053, 890.2, 1030.4, 1339, 1201, 1152, 1201, 609.86, 635.429999999999, 657.64, 593.62, 1370, 570.5, 610.1, 596.023370060814, 677.339443868788, 692.972323406659)</t>
@@ -727,13 +817,16 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(4, 215, 93, 121, 139, 72, 3, 73, 171, 214, 120, 91, 77, 216, 92, 106, 137)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(2, 74, 75, 76, 105, 109, 119, 122, 135, 140, 153, 154, 155, 156, 201, 202)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(3, 4, 72, 73, 77, 91, 92, 93, 106, 120, 121, 137, 139, 171, 214, 215, 216)</t>
+    <t xml:space="preserve">c(120, 214, 72, 119, 155, 140, 74, 135, 216, 91, 92, 121, 93, 202, 106, 153, 201)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2, 3, 4, 72, 73, 74, 75, 76, 77, 91, 92, 93, 105, 106, 109, 119, 120, 121, 122, 135, 137, 139, 140, 153, 154, 155, 156, 171, 201, 202, 214, 215, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2, 3, 4, 73, 75, 76, 77, 105, 109, 122, 137, 139, 154, 156, 171, 215)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(72, 74, 91, 92, 93, 106, 119, 120, 121, 135, 140, 153, 155, 201, 202, 214, 216)</t>
   </si>
   <si>
     <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
@@ -868,7 +961,7 @@
         MPinvS &lt;&lt;- t(X * weights)/sxtx
     X %*% (MPinvS/sxtx)
 })), offset = 849.657125373826, ustart = c(`21` = 8.92287462617401, `22` = 100.222874626174, `23` = 88.3828746261739, `853` = -313.657125373826, `854` = -158.657125373826, `855` = -449.657125373826, `856` = -387.657125373826, `857` = -242.657125373826, `858` = -488.657125373826, `1271` = 622.342874626174, `1272` = 583.342874626174, `1273` = 565.342874626174, `1374` = -309.157125373826, `1375` = -61.657125373826, `1378` = -183.857125373826, `1492` = 191.142874626174, `1493` = 203.342874626174, `1494` = 40.542874626174, 
-`1495` = 180.742874626174, `1586` = 489.342874626174, `1588` = 351.342874626174, `1590` = 302.342874626174, `1591` = 351.342874626174, `1732` = -239.797125373826, `1733` = -214.227125373827, `1734` = -192.017125373826, `1735` = -256.037125373826, `1778` = 520.342874626174, `1952` = -279.157125373826, `1967` = -239.557125373826, `1991` = -253.633755313012, `1992` = -172.317681505038, `1993` = -156.684801967167), control = list(mstop = 1100, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, 
+`1495` = 180.742874626174, `1586` = 489.342874626174, `1588` = 351.342874626174, `1590` = 302.342874626174, `1591` = 351.342874626174, `1732` = -239.797125373826, `1733` = -214.227125373827, `1734` = -192.017125373826, `1735` = -256.037125373826, `1778` = 520.342874626174, `1952` = -279.157125373826, `1967` = -239.557125373826, `1991` = -253.633755313012, `1992` = -172.317681505038, `1993` = -156.684801967167), control = list(mstop = 1000, nu = 0.1, risk = "inbag", stopintern = FALSE, center = TRUE, 
     trace = FALSE), family = new("boost_family_glm", fW = function (f) 
 return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
 y - f, risk = function (y, f, w = 1) 
@@ -1115,19 +1208,436 @@
 }, assign = 0:4, center = c(0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
   </si>
   <si>
-    <t xml:space="preserve">c(784.135187358325, 1038.3720447704, 907.158579007453, 566.899637053684, 707.091493413349, 433.326242841697, 482.2598344436, 560.366564765902, 291.819649165223, 1341.39520025624, 1303.82463735351, 1277.51061295474, 510.373581874945, 702.338347641223, 689.793030486946, 1092.48202787702, 1144.50710218657, 1013.92424953554, 1072.1383599465, 1341.02690166061, 1239.9064509851, 1223.25476668889, 1233.53372579618, 652.153482530738, 653.410874997568, 645.778878108062, 803.445878848607, 1262.44391031815, 
-614.555530644047, 554.553969701259, 589.709588690546, 716.169961867671, 654.799570287386)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(-74.4448126416754, 88.4920447704038, -30.8814209925472, 30.8996370536836, 16.091493413349, 33.3262428416971, 20.2598344435999, -46.6334352340978, -69.1803508347772, -130.604799743764, -129.175362646491, -137.489387045262, -30.1264181250548, -85.6616523587767, 23.9930304869459, 51.6820278770249, 91.5071021865679, 123.724249535538, 41.7383599465018, 2.0269016606087, 38.9064509850982, 71.2547666888902, 32.5337257961771, 42.2934825307376, 17.9808749975695, -11.8611218919377, 209.825878848607, -107.556089681852, 
-44.0555306440474, -55.5460302987407, -6.31378137026809, 38.8305179988828, -38.1727531192728)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(74.4448126416754, 88.4920447704038, 30.8814209925472, 30.8996370536836, 16.091493413349, 33.3262428416971, 20.2598344435999, 46.6334352340978, 69.1803508347772, 130.604799743764, 129.175362646491, 137.489387045262, 30.1264181250548, 85.6616523587767, 23.9930304869459, 51.6820278770249, 91.5071021865679, 123.724249535538, 41.7383599465018, 2.0269016606087, 38.9064509850982, 71.2547666888902, 32.5337257961771, 42.2934825307376, 17.9808749975695, 11.8611218919377, 209.825878848607, 107.556089681852, 
-44.0555306440474, 55.5460302987407, 6.31378137026809, 38.8305179988828, 38.1727531192728)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(119, 201, 122, 2, 109, 154, 155, 153, 156, 74, 75, 76, 140, 202, 105, 135)</t>
+    <t xml:space="preserve">c(784.739102829413, 1038.48994587503, 907.595027826887, 566.619481590319, 706.569201067324, 432.733547106262, 481.406700857378, 559.595484389867, 291.322870728187, 1339.08292527732, 1301.61041545327, 1275.19154922501, 508.635016644178, 704.069318194435, 692.062412973303, 1091.75981335754, 1143.45321927583, 1013.17899371699, 1071.61412857229, 1341.84681561795, 1240.76086590338, 1224.00212055493, 1234.25047858603, 654.424044012566, 655.566718039035, 648.17905825722, 805.854102458869, 1260.8798612819, 
+616.568959775515, 552.785974721061, 591.70668004738, 717.195866152052, 655.375310417026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(-73.8408971705866, 88.6099458750308, -30.4449721731132, 30.6194815903193, 15.5692010673235, 32.7335471062621, 19.4067008573779, -47.4045156101329, -69.6771292718126, -132.917074722683, -131.389584546732, -139.808450774994, -31.8649833558219, -83.9306818055647, 26.2624129733031, 50.959813357545, 90.4532192758318, 122.978993716994, 41.214128572291, 2.84681561794878, 39.7608659033826, 72.0021205549301, 33.2504785860276, 44.5640440125657, 20.1367180390358, -9.46094174277971, 212.234102458869, -109.120138718098, 
+46.0689597755154, -57.3140252789391, -4.3166900134338, 39.856422283264, -37.5970129896335)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(73.8408971705866, 88.6099458750308, 30.4449721731132, 30.6194815903193, 15.5692010673235, 32.7335471062621, 19.4067008573779, 47.4045156101329, 69.6771292718126, 132.917074722683, 131.389584546732, 139.808450774994, 31.8649833558219, 83.9306818055647, 26.2624129733031, 50.959813357545, 90.4532192758318, 122.978993716994, 41.214128572291, 2.84681561794878, 39.7608659033826, 72.0021205549301, 33.2504785860276, 44.5640440125657, 20.1367180390358, 9.46094174277971, 212.234102458869, 109.120138718098, 
+46.0689597755154, 57.3140252789391, 4.3166900134338, 39.856422283264, 37.5970129896335)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(156, 76, 154, 109, 105, 139, 137, 77, 4, 3, 73, 2, 215, 75, 122, 171)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(121, 216, 106, 105, 75, 155, 201, 122, 120, 2, 202, 135, 4, 153, 93, 214, 73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(3, 72, 74, 76, 77, 91, 92, 109, 119, 137, 139, 140, 154, 156, 171, 215)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2, 4, 73, 75, 93, 105, 106, 120, 121, 122, 135, 153, 155, 201, 202, 214, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(76, 171, 91, 77, 156, 92, 140, 119, 139, 3, 109, 74, 154, 72, 215, 137)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(858.58, 949.88, 938.04, 540.5, 788, 665.8, 609.86, 635.429999999999, 657.64, 593.62, 610.1, 596.023370060814, 677.339443868788, 692.972323406659)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_g_day + NDF_nutrition + CP_nutrition + NDF_digest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(155, 2, 156, 202, 109, 105, 154)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(3, 4, 106, 153, 214, 215, 216)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(2, 105, 109, 154, 155, 156, 202)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list(baselearner = list(list(model.frame = function () 
+return(NULL), get_data = function () 
+X, get_index = function () 
+index, get_vary = function () 
+NULL, get_names = function () 
+colnames(X), set_names = function (value) 
+attr(X, "colnames") &lt;&lt;- value, dpp = function (weights) 
+{
+    weights &lt;- weights[cc]
+    xtx &lt;- colSums(X^2 * weights, na.rm = TRUE)
+    xtx[xtx &lt; .Machine$double.eps] &lt;- 1
+    sxtx &lt;- sqrt(xtx)
+    p &lt;- ncol(X)
+    if (is(X, "Matrix")) {
+        MPinvS &lt;- t(X * weights)/sxtx
+        est &lt;- function(y) MPinvS %*% y
+    }
+    else {
+        MPinvS &lt;- NULL
+        storage.mode(X) &lt;- "double"
+        est &lt;- function(y) crossprod(X, y * weights)/sxtx
+    }
+    fit &lt;- function(y) {
+        if (!is.null(index)) 
+            y &lt;- y[cc]
+        mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
+        xselect &lt;- which(as.logical(mmu == amu))[1]
+        coef &lt;- mu[xselect]/sxtx[xselect]
+        ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
+            if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
+            return(coef * X[index, xselect, drop = FALSE])
+        })
+        class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
+        return(ret)
+    }
+    predict &lt;- function(bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) {
+        aggregate &lt;- match.arg(aggregate)
+        cf &lt;- switch(aggregate, sum = {
+            cf &lt;- rep(0, bm[[1]]$model["p"])
+            for (i in 1:length(bm)) {
+                m &lt;- bm[[i]]$model
+                cf[m[2]] &lt;- cf[m[2]] + m[1]
+            }
+            cf
+        }, cumsum = {
+            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+            if (length(bm) &gt; 2) {
+                for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
+            }
+            cf
+        }, none = {
+            cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+            if (length(bm) &gt; 2) {
+                for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
+            }
+            cf
+        })
+        if (!is.null(newdata)) {
+            stopifnot(all(class(newdata) == class(X)))
+            stopifnot(all(colnames(newdata) == colnames(X)))
+            X &lt;- newdata
+            return(X %*% cf)
+        }
+        if (!is.null(index)) 
+            return(X[index, , drop = FALSE] %*% cf)
+        return(X %*% cf)
+    }
+    ret &lt;- list(fit = fit, predict = predict, Xnames = colnames(X), MPinv = function() {
+        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
+        return(MPinvS/sxtx)
+    }, hatvalues = function() {
+        if (is.null(MPinvS)) MPinvS &lt;&lt;- t(X * weights)/sxtx
+        X %*% (MPinvS/sxtx)
+    })
+    class(ret) &lt;- c("bl_cwlin", "bl")
+    return(ret)
+})), basemodel = list(list(fit = function (y) 
+{
+    if (!is.null(index)) 
+        y &lt;- y[cc]
+    mmu &lt;- max(amu &lt;- abs(mu &lt;- est(y)))
+    xselect &lt;- which(as.logical(mmu == amu))[1]
+    coef &lt;- mu[xselect]/sxtx[xselect]
+    ret &lt;- list(model = c(coef = coef, xselect = xselect, p = p), fitted = function() {
+        if (is.null(index)) return(coef * X[, xselect, drop = FALSE])
+        return(coef * X[index, xselect, drop = FALSE])
+    })
+    class(ret) &lt;- c("bm_cwlin", "bm_lin", "bm")
+    return(ret)
+}, predict = function (bm, newdata = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    aggregate &lt;- match.arg(aggregate)
+    cf &lt;- switch(aggregate, sum = {
+        cf &lt;- rep(0, bm[[1]]$model["p"])
+        for (i in 1:length(bm)) {
+            m &lt;- bm[[i]]$model
+            cf[m[2]] &lt;- cf[m[2]] + m[1]
+        }
+        cf
+    }, cumsum = {
+        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+        if (length(bm) &gt; 2) {
+            for (i in 2:length(bm)) cf &lt;- cbind(cf, cf[[i - 1]] + coef(bm[[i]], all = TRUE))
+        }
+        cf
+    }, none = {
+        cf &lt;- matrix(coef(bm[[1]], all = TRUE), ncol = 1)
+        if (length(bm) &gt; 2) {
+            for (i in 2:length(bm)) cf &lt;- cbind(cf, coef(bm[[i]], all = TRUE))
+        }
+        cf
+    })
+    if (!is.null(newdata)) {
+        stopifnot(all(class(newdata) == class(X)))
+        stopifnot(all(colnames(newdata) == colnames(X)))
+        X &lt;- newdata
+        return(X %*% cf)
+    }
+    if (!is.null(index)) 
+        return(X[index, , drop = FALSE] %*% cf)
+    return(X %*% cf)
+}, Xnames = c("(Intercept)", "bw_kg", "adg_g_day", "NDF_nutrition", "CP_nutrition", "NDF_digest"), MPinv = function () 
+{
+    if (is.null(MPinvS)) 
+        MPinvS &lt;&lt;- t(X * weights)/sxtx
+    return(MPinvS/sxtx)
+}, hatvalues = function () 
+{
+    if (is.null(MPinvS)) 
+        MPinvS &lt;&lt;- t(X * weights)/sxtx
+    X %*% (MPinvS/sxtx)
+})), offset = 700.984652666876, ustart = c(`21` = 157.595347333124, `22` = 248.895347333124, `23` = 237.055347333124, `1374` = -160.484652666876, `1375` = 87.0153473331244, `1378` = -35.1846526668756, `1732` = -91.1246526668756, `1733` = -65.5546526668766, `1734` = -43.3446526668756, `1735` = -107.364652666876, `1967` = -90.8846526668756, `1991` = -104.961282606062, `1992` = -23.6452087980877, `1993` = -8.01232926021657), control = list(mstop = 1000, nu = 0.1, risk = "inbag", stopintern = FALSE, 
+    center = TRUE, trace = FALSE), family = new("boost_family_glm", fW = function (f) 
+return(rep(1, length = length(f))), ngradient = function (y, f, w = 1) 
+y - f, risk = function (y, f, w = 1) 
+sum(w * loss(y, f), na.rm = TRUE), offset = function (x, w, ...) 
+UseMethod("weighted.mean"), check_y = function (y) 
+{
+    if (!is.numeric(y) || !is.null(dim(y))) 
+        stop("response is not a numeric vector but ", sQuote("family = Gaussian()"))
+    y
+}, weights = function (w) 
+{
+    switch(weights, any = TRUE, none = isTRUE(all.equal(unique(w), 1)), zeroone = isTRUE(all.equal(unique(w + abs(w - 1)), 1)), case = isTRUE(all.equal(unique(w - floor(w)), 0)))
+}, nuisance = function () 
+return(NA), response = function (f) 
+f, rclass = function (f) 
+NA, name = "Squared Error (Regression)", charloss = "(y - f)^2 \n"), response = c(`21` = 858.58, `22` = 949.88, `23` = 938.04, `1374` = 540.5, `1375` = 788, `1378` = 665.8, `1732` = 609.86, `1733` = 635.429999999999, `1734` = 657.64, `1735` = 593.62, `1967` = 610.1, `1991` = 596.023370060814, `1992` = 677.339443868788, `1993` = 692.972323406659), rownames = c("21", "22", "23", "1374", "1375", "1378", "1732", "1733", "1734", "1735", "1967", "1991", "1992", "1993"), `(weights)` = c(1, 1, 1, 1, 1, 1, 
+1, 1, 1, 1, 1, 1, 1, 1), nuisance = function () 
+nuisance, update = function (weights = NULL, oobweights = NULL, risk = "oobag", trace = NULL) 
+{
+    res &lt;- update(weights = weights, oobweights = oobweights, risk = risk, trace = trace)
+    res$newX &lt;- newX
+    res$assign &lt;- assign
+    res$center &lt;- cm
+    res$call &lt;- cl
+    res$hatvalues &lt;- function() {
+        H &lt;- vector(mode = "list", length = ncol(X))
+        MPinv &lt;- res$basemodel[[1]]$MPinv()
+        for (j in unique(res$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
+        H
+    }
+    res$rownames &lt;- rownames(mf)
+    res$model.frame &lt;- function(which = NULL) {
+        if (!is.null(which)) 
+            warning("Argument ", sQuote("which"), " is ignored")
+        mf
+    }
+    class(res) &lt;- c("glmboost", "mboost")
+    res
+}, mstop = function () 
+mstop, xselect = function () 
+{
+    if (mstop == 0) 
+        return(NULL)
+    return(xselect[1:mstop])
+}, fitted = function () 
+as.vector(fit), resid = function () 
+u, risk = function () 
+{
+    mrisk[1:(mstop + 1)]
+}, logLik = function () 
+-mrisk[mstop + 1], which = function (which = NULL, usedonly = FALSE) 
+{
+    if (is.null(which)) 
+        which &lt;- 1:length(bnames)
+    if (is.character(which)) {
+        i &lt;- sapply(which, function(w) {
+            wi &lt;- grep(w, bnames, fixed = TRUE)
+            if (length(wi) &gt; 0) 
+                return(wi)
+            return(NA)
+        })
+        if (any(is.na(i))) 
+            warning(paste(which[is.na(i)], collapse = ","), " not found")
+        which &lt;- i
+    }
+    if (usedonly) 
+        which &lt;- which[which %in% RET$xselect()]
+    return(which)
+}, predict = function (newdata = NULL, which = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    if (mstop == 0) {
+        if (length(offset) == 1) {
+            if (!is.null(newdata)) 
+                return(rep(offset, NROW(newdata)))
+            return(rep(offset, NROW(y)))
+        }
+        if (!is.null(newdata)) {
+            warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
+            return(rep(0, NCOL(newdata)))
+        }
+        return(offset)
+    }
+    if (!is.null(xselect)) 
+        indx &lt;- ((1:length(xselect)) &lt;= mstop)
+    which &lt;- thiswhich(which, usedonly = nw &lt;- is.null(which))
+    if (length(which) == 0) 
+        return(NULL)
+    aggregate &lt;- match.arg(aggregate)
+    pfun &lt;- function(w, agg) {
+        ix &lt;- xselect == w &amp; indx
+        if (!any(ix)) 
+            return(0)
+        if (cwlin) 
+            w &lt;- 1
+        ret &lt;- nu * bl[[w]]$predict(ens[ix], newdata = newdata, aggregate = agg)
+        if (agg == "sum") 
+            return(ret)
+        m &lt;- Matrix(0, nrow = nrow(ret), ncol = sum(indx))
+        m[, which(ix)] &lt;- ret
+        m
+    }
+    pr &lt;- switch(aggregate, sum = {
+        pr &lt;- lapply(which, pfun, agg = "sum")
+        if (!nw) {
+            if (NCOL(pr[[1]]) == 1) {
+                pr &lt;- do.call("cbind", pr)
+                colnames(pr) &lt;- bnames[which]
+                attr(pr, "offset") &lt;- offset
+            }
+            return(pr)
+        } else {
+            ret &lt;- Reduce("+", pr)
+            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
+                warning("User-specified offset is not a scalar, ", "thus it cannot be used for predictions when ", sQuote("newdata"), " is specified.")
+            } else {
+                ret &lt;- ret + offset
+            }
+            return(ret)
+        }
+    }, cumsum = {
+        if (!nw) {
+            pr &lt;- lapply(which, pfun, agg = "none")
+            pr &lt;- lapply(pr, function(x) {
+                .Call("R_mcumsum", as(x, "matrix"), PACKAGE = "mboost")
+            })
+            names(pr) &lt;- bnames[which]
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        } else {
+            pr &lt;- 0
+            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
+            pr &lt;- .Call("R_mcumsum", as(pr, "matrix"), PACKAGE = "mboost")
+            if (length(offset) != 1 &amp;&amp; !is.null(newdata)) {
+                warning(sQuote("length(offset) &gt; 1"), ": User-specified offset is not a scalar, ", "thus offset not used for prediction when ", sQuote("newdata"), " is specified")
+            } else {
+                pr &lt;- pr + offset
+            }
+            return(pr)
+        }
+    }, none = {
+        if (!nw) {
+            pr &lt;- lapply(which, pfun, agg = "none")
+            for (i in 1:length(pr)) pr[[i]] &lt;- as(pr[[i]], "matrix")
+            names(pr) &lt;- bnames[which]
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        } else {
+            pr &lt;- 0
+            for (i in 1:max(xselect)) pr &lt;- pr + pfun(i, agg = "none")
+            pr &lt;- as(pr, "matrix")
+            attr(pr, "offset") &lt;- offset
+            return(pr)
+        }
+    })
+    return(pr)
+}, model.frame = function (which = NULL) 
+{
+    if (!is.null(which)) 
+        warning("Argument ", sQuote("which"), " is ignored")
+    mf
+}, subset = function (i) 
+{
+    if (i &lt;= mstop || i &lt;= length(xselect)) {
+        if (i != mstop) {
+            mstop &lt;&lt;- i
+            fit &lt;&lt;- RET$predict()
+            u &lt;&lt;- ngradient(y, fit, weights)
+        }
+    }
+    else {
+        if (mstop != length(xselect)) {
+            mstop &lt;&lt;- length(xselect)
+            fit &lt;&lt;- RET$predict()
+            u &lt;&lt;- ngradient(y, fit, weights)
+        }
+        tmp &lt;- boost(i - mstop)
+    }
+}, coef = function (which = NULL, aggregate = c("sum", "cumsum", "none")) 
+{
+    if (!is.null(xselect)) 
+        indx &lt;- ((1:length(xselect)) &lt;= mstop)
+    which &lt;- thiswhich(which, usedonly = is.null(which))
+    if (length(which) == 0) 
+        return(NULL)
+    aggregate &lt;- match.arg(aggregate)
+    cfun &lt;- function(w) {
+        ix &lt;- (xselect == w &amp; indx)
+        cf &lt;- numeric(mstop)
+        if (!any(ix)) {
+            if (!cwlin) {
+                nm &lt;- bl[[w]]$Xnames
+                cf &lt;- matrix(0, nrow = length(nm), ncol = mstop)
+            }
+        }
+        else {
+            if (inherits(ens[ix][[1]], "bm_cwlin") &amp;&amp; !cwlin) {
+                cftmp &lt;- sapply(ens[ix], coef, all = TRUE)
+            }
+            else {
+                cftmp &lt;- sapply(ens[ix], coef)
+            }
+            nr &lt;- NROW(cftmp)
+            if (!is.matrix(cftmp)) 
+                nr &lt;- 1
+            cf &lt;- matrix(0, nrow = nr, ncol = mstop)
+            cf[, which(ix)] &lt;- cftmp
+        }
+        if (!is.matrix(cf)) 
+            cf &lt;- matrix(cf, nrow = 1)
+        if (any(sapply(cf, is.null))) {
+            ret &lt;- NULL
+        }
+        else {
+            ret &lt;- switch(aggregate, sum = rowSums(cf) * nu, cumsum = {
+                .Call("R_mcumsum", as(cf, "matrix") * nu, PACKAGE = "mboost")
+            }, none = nu * cf)
+        }
+        if (!cwlin) {
+            nm &lt;- bl[[w]]$Xnames
+            if (is.matrix(ret)) {
+                rownames(ret) &lt;- nm
+            }
+            else {
+                names(ret) &lt;- nm
+            }
+        }
+        ret
+    }
+    ret &lt;- lapply(which, cfun)
+    names(ret) &lt;- bnames[which]
+    attr(ret, "offset") &lt;- offset
+    return(ret)
+}, hatvalues = function () 
+{
+    H &lt;- vector(mode = "list", length = ncol(X))
+    MPinv &lt;- ret$basemodel[[1]]$MPinv()
+    for (j in unique(ret$xselect())) H[[j]] &lt;- (X[, j] %*% MPinv[j, , drop = FALSE]) * control$nu
+    H
+}, newX = function (newdata) 
+{
+    mf &lt;- model.frame(delete.response(attr(mf, "terms")), data = newdata, na.action = na.action)
+    X &lt;- model.matrix(delete.response(attr(mf, "terms")), data = mf, contrasts.arg = contrasts.arg)
+    scale(X, center = cm, scale = FALSE)
+}, assign = 0:5, center = c(0, 0, 0, 0, 0, 0), call = glmboost.formula(formula = form, data = data, family = family, center = FALSE, control = boost_control(mstop = mstop, nu = nu)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(819.848409424925, 986.82097003355, 921.572662061683, 575.837215981887, 678.257060671617, 681.10767399932, 652.479103706235, 652.94533151273, 661.564309643787, 641.054580572059, 565.953409596184, 606.640552984356, 697.812349625307, 682.108280617438)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(-38.7315905750755, 36.9409700335503, -16.4673379383166, 35.3372159818872, -109.742939328383, 15.3076739993196, 42.6191037062347, 17.5153315127314, 3.92430964378741, 47.4345805720594, -44.1465904038164, 10.6171829235425, 20.4729057565195, -10.8640427892212)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(38.7315905750755, 36.9409700335503, 16.4673379383166, 35.3372159818872, 109.742939328383, 15.3076739993196, 42.6191037062347, 17.5153315127314, 3.92430964378741, 47.4345805720594, 44.1465904038164, 10.6171829235425, 20.4729057565195, 10.8640427892212)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(3, 4, 153, 106, 215, 216, 214)</t>
   </si>
 </sst>
 </file>
@@ -1730,6 +2240,96 @@
       <c r="CM1" t="s">
         <v>90</v>
       </c>
+      <c r="CN1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>102</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DB1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DC1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DD1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DE1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DG1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DH1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DK1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DL1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DM1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DN1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DO1" t="s">
+        <v>118</v>
+      </c>
+      <c r="DP1" t="s">
+        <v>119</v>
+      </c>
+      <c r="DQ1" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2"/>
@@ -1737,77 +2337,77 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I2" t="n">
         <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>0.762219264627017</v>
+        <v>0.884339681598727</v>
       </c>
       <c r="K2" t="n">
-        <v>13.7040621779351</v>
+        <v>11.3539707148221</v>
       </c>
       <c r="L2" t="n">
-        <v>0.909924804648278</v>
+        <v>0.949993912040946</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.787062936227441</v>
+        <v>0.884339681598727</v>
       </c>
       <c r="O2" t="n">
-        <v>13.4602879881062</v>
+        <v>11.3539707148221</v>
       </c>
       <c r="P2" t="n">
-        <v>0.919020844060638</v>
+        <v>0.949993912040946</v>
       </c>
       <c r="Q2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.762219264627017</v>
+        <v>0.884339681598727</v>
       </c>
       <c r="S2" t="n">
-        <v>13.7040621779351</v>
+        <v>11.3539707148221</v>
       </c>
       <c r="T2" t="n">
-        <v>0.909924804648278</v>
+        <v>0.949993912040946</v>
       </c>
       <c r="U2" t="n">
-        <v>0.210566005679763</v>
+        <v>0.0144351518759163</v>
       </c>
       <c r="V2" t="n">
-        <v>3.68176595003665</v>
+        <v>0.993170292647946</v>
       </c>
       <c r="W2"/>
       <c r="X2" t="n">
-        <v>-312.489584456521</v>
+        <v>-298.962349446351</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.6262640064568</v>
+        <v>9.39986609082291</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.57822951461177</v>
+        <v>2.50631330473245</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.306704222682844</v>
+        <v>-0.295044747385717</v>
       </c>
       <c r="AB2" t="e">
         <v>#NUM!</v>
@@ -1816,133 +2416,133 @@
         <v>#NUM!</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.911111915130543</v>
+        <v>0.894546875377645</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.877545509618388</v>
+        <v>0.852280755682572</v>
       </c>
       <c r="AF2" t="n">
-        <v>11.1006605079224</v>
+        <v>10.6516932660177</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.6964310831701</v>
+        <v>12.2650053212217</v>
       </c>
       <c r="AH2" t="n">
-        <v>-337.778699660107</v>
+        <v>-330.06320434352</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.3582409911919</v>
+        <v>10.5853537165578</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.84736931196352</v>
+        <v>2.58657627029663</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.0637889612714265</v>
+        <v>-0.25831075279214</v>
       </c>
       <c r="AL2"/>
       <c r="AM2"/>
       <c r="AN2" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="AO2"/>
       <c r="AP2" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="AQ2"/>
       <c r="AR2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="AS2"/>
       <c r="AT2" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AU2"/>
       <c r="AV2" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AW2" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AX2" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="AY2"/>
       <c r="AZ2" t="n">
         <v>18</v>
       </c>
       <c r="BA2" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BB2" t="n">
         <v>35</v>
       </c>
       <c r="BC2" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="BD2" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="BE2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="BF2" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="BG2" t="n">
-        <v>-337.778699660107</v>
+        <v>-330.06320434352</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.3582409911919</v>
+        <v>10.5853537165578</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.84736931196352</v>
+        <v>2.58657627029663</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.0637889612714265</v>
+        <v>-0.25831075279214</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.0637889612714265</v>
+        <v>-0.25831075279214</v>
       </c>
       <c r="BL2" t="n">
-        <v>459.972580767861</v>
+        <v>521.21693232746</v>
       </c>
       <c r="BM2" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="BN2" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="BO2" t="n">
-        <v>-323.649270474329</v>
+        <v>-305.133940925641</v>
       </c>
       <c r="BP2" t="n">
-        <v>9.8621998498151</v>
+        <v>9.50776632274425</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.50782785674312</v>
+        <v>2.49495203534041</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.264793657084304</v>
+        <v>-0.285241263403289</v>
       </c>
       <c r="BS2"/>
       <c r="BT2"/>
       <c r="BU2" t="n">
-        <v>797.751280427968</v>
+        <v>851.28013667098</v>
       </c>
       <c r="BV2" t="n">
-        <v>474.102009953638</v>
+        <v>546.146195745339</v>
       </c>
       <c r="BW2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="BX2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="BY2" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="BZ2" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="CA2" t="n">
         <v>0.155946259824747</v>
@@ -1950,31 +2550,105 @@
       <c r="CB2" t="n">
         <v>-0.522514820180757</v>
       </c>
-      <c r="CC2"/>
+      <c r="CC2" t="n">
+        <v>6133.10581746637</v>
+      </c>
       <c r="CD2" t="n">
-        <v>459.972580767861</v>
+        <v>2920.60300502954</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.964421663874353</v>
-      </c>
-      <c r="CF2"/>
-      <c r="CG2" t="n">
+        <v>61295.3450864414</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>24810.1466809275</v>
+      </c>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2" t="n">
+        <v>0.0644510018941835</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.0306917564137314</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.644134720620697</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.260722521071389</v>
+      </c>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2" t="n">
+        <v>521.21693232746</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.957260554947852</v>
+      </c>
+      <c r="CR2"/>
+      <c r="CS2" t="n">
         <v>1</v>
       </c>
-      <c r="CH2" t="n">
-        <v>35.7642097013271</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>7.45010959508121</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0.380621151589194</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0.343534057195433</v>
-      </c>
-      <c r="CL2"/>
-      <c r="CM2"/>
+      <c r="CT2" t="n">
+        <v>43.9832507969739</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.67653267833978</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.113508974457149</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0.051949713354377</v>
+      </c>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2" t="n">
+        <v>5105.32763100361</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>2338.5180062922</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>59146.6224210591</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>24433.4546226336</v>
+      </c>
+      <c r="DD2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DE2"/>
+      <c r="DF2" t="n">
+        <v>0.0556897260782081</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.0254532576703248</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.650061311103162</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.268795705148305</v>
+      </c>
+      <c r="DJ2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DK2"/>
+      <c r="DL2" t="n">
+        <v>1453.49785040685</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>823.192499668267</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>3038.75273516219</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>532.723017677578</v>
+      </c>
+      <c r="DP2"/>
+      <c r="DQ2"/>
     </row>
     <row r="3">
       <c r="A3"/>
@@ -1982,77 +2656,77 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I3" t="n">
         <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.762219264627017</v>
+        <v>0.884339681598727</v>
       </c>
       <c r="K3" t="n">
-        <v>13.7040621779351</v>
+        <v>11.3539707148221</v>
       </c>
       <c r="L3" t="n">
-        <v>0.909924804648278</v>
+        <v>0.949993912040946</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.787062936227441</v>
+        <v>0.884339681598727</v>
       </c>
       <c r="O3" t="n">
-        <v>13.4602879881062</v>
+        <v>11.3539707148221</v>
       </c>
       <c r="P3" t="n">
-        <v>0.919020844060638</v>
+        <v>0.949993912040946</v>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.762219264627017</v>
+        <v>0.884339681598727</v>
       </c>
       <c r="S3" t="n">
-        <v>13.7040621779351</v>
+        <v>11.3539707148221</v>
       </c>
       <c r="T3" t="n">
-        <v>0.909924804648278</v>
+        <v>0.949993912040946</v>
       </c>
       <c r="U3" t="n">
-        <v>0.210566005679763</v>
+        <v>0.0144351518759163</v>
       </c>
       <c r="V3" t="n">
-        <v>3.68176595003665</v>
+        <v>0.993170292647946</v>
       </c>
       <c r="W3"/>
       <c r="X3" t="n">
-        <v>-312.489584456521</v>
+        <v>-298.962349446351</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.6262640064568</v>
+        <v>9.39986609082291</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.57822951461177</v>
+        <v>2.50631330473245</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.306704222682844</v>
+        <v>-0.295044747385717</v>
       </c>
       <c r="AB3" t="e">
         <v>#NUM!</v>
@@ -2061,133 +2735,133 @@
         <v>#NUM!</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.613326614123491</v>
+        <v>0.874132487819809</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.749648209411679</v>
+        <v>0.845891626179988</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.3074638479477</v>
+        <v>12.0562481636265</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.8038729287295</v>
+        <v>13.1078460912725</v>
       </c>
       <c r="AH3" t="n">
-        <v>-287.200469252935</v>
+        <v>-267.861494549182</v>
       </c>
       <c r="AI3" t="n">
-        <v>15.8942870217217</v>
+        <v>8.21437846508801</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.30908971726002</v>
+        <v>2.42605033916827</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.549619484094262</v>
+        <v>-0.331778741979295</v>
       </c>
       <c r="AL3"/>
       <c r="AM3"/>
       <c r="AN3" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="AO3"/>
       <c r="AP3" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="AQ3"/>
       <c r="AR3" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="AS3"/>
       <c r="AT3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AU3"/>
       <c r="AV3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AW3" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AX3" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="AY3"/>
       <c r="AZ3" t="n">
         <v>17</v>
       </c>
       <c r="BA3" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BB3" t="n">
         <v>35</v>
       </c>
       <c r="BC3" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="BD3" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="BE3" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="BF3" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="BG3" t="n">
-        <v>-287.200469252935</v>
+        <v>-267.861494549182</v>
       </c>
       <c r="BH3" t="n">
-        <v>15.8942870217217</v>
+        <v>8.21437846508801</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.30908971726002</v>
+        <v>2.42605033916827</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0.549619484094262</v>
+        <v>-0.331778741979295</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.549619484094262</v>
+        <v>-0.331778741979295</v>
       </c>
       <c r="BL3" t="n">
-        <v>602.128051305999</v>
+        <v>570.911995113574</v>
       </c>
       <c r="BM3" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="BN3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="BO3" t="n">
-        <v>-323.649270474329</v>
+        <v>-305.133940925641</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.8621998498151</v>
+        <v>9.50776632274425</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.50782785674312</v>
+        <v>2.49495203534041</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.264793657084304</v>
+        <v>-0.285241263403289</v>
       </c>
       <c r="BS3"/>
       <c r="BT3"/>
       <c r="BU3" t="n">
-        <v>889.328520558934</v>
+        <v>838.773489662756</v>
       </c>
       <c r="BV3" t="n">
-        <v>565.679250084605</v>
+        <v>533.639548737114</v>
       </c>
       <c r="BW3" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="BX3" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="BY3" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="BZ3" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="CA3" t="n">
         <v>0.155946259824747</v>
@@ -2195,31 +2869,105 @@
       <c r="CB3" t="n">
         <v>-0.522514820180757</v>
       </c>
-      <c r="CC3"/>
+      <c r="CC3" t="n">
+        <v>4077.54944454086</v>
+      </c>
       <c r="CD3" t="n">
-        <v>602.128051305999</v>
+        <v>1756.43300755487</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.855427945422203</v>
-      </c>
-      <c r="CF3"/>
-      <c r="CG3" t="n">
+        <v>56997.8997556767</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>24056.7625643396</v>
+      </c>
+      <c r="CG3"/>
+      <c r="CH3"/>
+      <c r="CI3" t="n">
+        <v>0.0469284502622327</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.0202147589269181</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.655987901585627</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0.276868889225222</v>
+      </c>
+      <c r="CM3"/>
+      <c r="CN3"/>
+      <c r="CO3"/>
+      <c r="CP3" t="n">
+        <v>570.911995113574</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>0.94272726913404</v>
+      </c>
+      <c r="CR3"/>
+      <c r="CS3" t="n">
         <v>1</v>
       </c>
-      <c r="CH3" t="n">
-        <v>35.7642097013271</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>7.45010959508121</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>0.380621151589194</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>0.343534057195433</v>
-      </c>
-      <c r="CL3"/>
-      <c r="CM3"/>
+      <c r="CT3" t="n">
+        <v>43.9832507969739</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.67653267833978</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0.113508974457149</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>0.051949713354377</v>
+      </c>
+      <c r="CX3"/>
+      <c r="CY3"/>
+      <c r="CZ3" t="n">
+        <v>5105.32763100361</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>2338.5180062922</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>59146.6224210591</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>24433.4546226336</v>
+      </c>
+      <c r="DD3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DE3"/>
+      <c r="DF3" t="n">
+        <v>0.0556897260782081</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0.0254532576703248</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>0.650061311103162</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0.268795705148305</v>
+      </c>
+      <c r="DJ3" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DK3"/>
+      <c r="DL3" t="n">
+        <v>1453.49785040685</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>823.192499668267</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>3038.75273516219</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>532.723017677578</v>
+      </c>
+      <c r="DP3"/>
+      <c r="DQ3"/>
     </row>
     <row r="4">
       <c r="A4"/>
@@ -2227,216 +2975,216 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1099</v>
+        <v>1000</v>
       </c>
       <c r="I4" t="n">
         <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.787062936227441</v>
+        <v>0.870923560652896</v>
       </c>
       <c r="K4" t="n">
-        <v>13.4602879881062</v>
+        <v>11.5401235132199</v>
       </c>
       <c r="L4" t="n">
-        <v>0.919020844060638</v>
+        <v>0.948655692016562</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.787062936227441</v>
+        <v>0.884339681598727</v>
       </c>
       <c r="O4" t="n">
-        <v>13.4602879881062</v>
+        <v>11.3539707148221</v>
       </c>
       <c r="P4" t="n">
-        <v>0.919020844060638</v>
+        <v>0.949993912040946</v>
       </c>
       <c r="Q4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.787062936227441</v>
+        <v>0.870923560652896</v>
       </c>
       <c r="S4" t="n">
-        <v>13.4602879881062</v>
+        <v>11.5401235132199</v>
       </c>
       <c r="T4" t="n">
-        <v>0.919020844060638</v>
+        <v>0.948655692016562</v>
       </c>
       <c r="U4" t="n">
-        <v>0.125079459033331</v>
+        <v>0.0403907005217045</v>
       </c>
       <c r="V4" t="n">
-        <v>2.18293875776426</v>
+        <v>1.25403905636718</v>
       </c>
       <c r="W4"/>
       <c r="X4" t="n">
-        <v>-105.51503482089</v>
+        <v>-158.663563155554</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.5245224660039</v>
+        <v>7.47144987614345</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.5114820231578</v>
+        <v>2.6033580854108</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.369277981064555</v>
+        <v>-0.287910276199468</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.770506874595163</v>
+        <v>-0.729271932420284</v>
       </c>
       <c r="AC4" t="e">
         <v>#NUM!</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.819898428456577</v>
+        <v>0.902037672421978</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.759612412931862</v>
+        <v>0.860439658698559</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.7152349701327</v>
+        <v>10.3859697837894</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.2221434076062</v>
+        <v>13.700635169847</v>
       </c>
       <c r="AH4" t="n">
-        <v>-142.318189747531</v>
+        <v>-175.570374451804</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.27025688682564</v>
+        <v>8.68413009976459</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.62081081038763</v>
+        <v>2.36971269811086</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.106387851760303</v>
+        <v>-0.279631085168225</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.41452081432434</v>
+        <v>-0.429879735411124</v>
       </c>
       <c r="AM4"/>
       <c r="AN4" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="AO4"/>
       <c r="AP4" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AQ4"/>
       <c r="AR4" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="AS4"/>
       <c r="AT4" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="AU4"/>
       <c r="AV4" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AW4" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AX4" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="AY4"/>
       <c r="AZ4" t="n">
         <v>17</v>
       </c>
       <c r="BA4" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BB4" t="n">
         <v>33</v>
       </c>
       <c r="BC4" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="BD4" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="BE4" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="BF4" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="BG4" t="n">
-        <v>-142.318189747531</v>
+        <v>-175.570374451804</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.27025688682564</v>
+        <v>8.68413009976459</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62081081038763</v>
+        <v>2.36971269811086</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.106387851760303</v>
+        <v>-0.279631085168225</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.106387851760303</v>
+        <v>-0.279631085168225</v>
       </c>
       <c r="BL4" t="n">
-        <v>596.571185252468</v>
+        <v>620.278965789995</v>
       </c>
       <c r="BM4" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="BN4" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="BO4" t="n">
-        <v>-226.816450335612</v>
+        <v>-215.414438128014</v>
       </c>
       <c r="BP4" t="n">
-        <v>10.9778486790247</v>
+        <v>10.7352268606284</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.56973977682172</v>
+        <v>2.56208950777438</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.319189568186482</v>
+        <v>-0.330661412222654</v>
       </c>
       <c r="BS4" t="n">
         <v>-0.635612592670827</v>
       </c>
       <c r="BT4"/>
       <c r="BU4" t="n">
-        <v>738.889375</v>
+        <v>795.849340241799</v>
       </c>
       <c r="BV4" t="n">
-        <v>512.072924664388</v>
+        <v>580.434902113785</v>
       </c>
       <c r="BW4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="BX4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="BY4" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="BZ4" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="CA4" t="n">
         <v>0.159942318730386</v>
@@ -2444,33 +3192,113 @@
       <c r="CB4" t="n">
         <v>-0.549828150540717</v>
       </c>
-      <c r="CC4"/>
+      <c r="CC4" t="n">
+        <v>1772.09942407647</v>
+      </c>
       <c r="CD4" t="n">
-        <v>596.571185252468</v>
+        <v>1506.57234404136</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.925350886250222</v>
-      </c>
-      <c r="CF4"/>
+        <v>48325.0835882834</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>18374.4282418291</v>
+      </c>
       <c r="CG4" t="n">
+        <v>1821.75837512059</v>
+      </c>
+      <c r="CH4"/>
+      <c r="CI4" t="n">
+        <v>0.0246810704211181</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.0209829186853735</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.673051847398701</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.255911463670109</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.0253726998246983</v>
+      </c>
+      <c r="CN4"/>
+      <c r="CO4"/>
+      <c r="CP4" t="n">
+        <v>620.278965789995</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.957778723065005</v>
+      </c>
+      <c r="CR4"/>
+      <c r="CS4" t="n">
         <v>1</v>
       </c>
-      <c r="CH4" t="n">
-        <v>52.0475208353742</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>6.01644008001093</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>0.154614253658224</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>0.371782786276091</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>0.503440314450764</v>
-      </c>
-      <c r="CM4"/>
+      <c r="CT4" t="n">
+        <v>23.9098418316386</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1.71498881906665</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.330424475505496</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.0117085442418624</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0.423404505479032</v>
+      </c>
+      <c r="CY4"/>
+      <c r="CZ4" t="n">
+        <v>1403.18434928644</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1222.8294336542</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>61881.7098337291</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>19282.1868101002</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>9994.44911681635</v>
+      </c>
+      <c r="DE4"/>
+      <c r="DF4" t="n">
+        <v>0.016807496425324</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.0145473306522012</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.662340612080334</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.215155173177175</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.0911493876649658</v>
+      </c>
+      <c r="DK4"/>
+      <c r="DL4" t="n">
+        <v>521.724702131946</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>401.273072096738</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>19171.9646963323</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>1283.76447860938</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>11557.9300879872</v>
+      </c>
+      <c r="DQ4"/>
     </row>
     <row r="5">
       <c r="A5"/>
@@ -2478,216 +3306,216 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1099</v>
+        <v>1000</v>
       </c>
       <c r="I5" t="n">
         <v>0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.787062936227441</v>
+        <v>0.870923560652896</v>
       </c>
       <c r="K5" t="n">
-        <v>13.4602879881062</v>
+        <v>11.5401235132199</v>
       </c>
       <c r="L5" t="n">
-        <v>0.919020844060638</v>
+        <v>0.948655692016562</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.787062936227441</v>
+        <v>0.884339681598727</v>
       </c>
       <c r="O5" t="n">
-        <v>13.4602879881062</v>
+        <v>11.3539707148221</v>
       </c>
       <c r="P5" t="n">
-        <v>0.919020844060638</v>
+        <v>0.949993912040946</v>
       </c>
       <c r="Q5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.787062936227441</v>
+        <v>0.870923560652896</v>
       </c>
       <c r="S5" t="n">
-        <v>13.4602879881062</v>
+        <v>11.5401235132199</v>
       </c>
       <c r="T5" t="n">
-        <v>0.919020844060638</v>
+        <v>0.948655692016562</v>
       </c>
       <c r="U5" t="n">
-        <v>0.125079459033331</v>
+        <v>0.0403907005217045</v>
       </c>
       <c r="V5" t="n">
-        <v>2.18293875776426</v>
+        <v>1.25403905636718</v>
       </c>
       <c r="W5"/>
       <c r="X5" t="n">
-        <v>-105.51503482089</v>
+        <v>-158.663563155554</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.5245224660039</v>
+        <v>7.47144987614345</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.5114820231578</v>
+        <v>2.6033580854108</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.369277981064555</v>
+        <v>-0.287910276199468</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.770506874595163</v>
+        <v>-0.729271932420284</v>
       </c>
       <c r="AC5" t="e">
         <v>#NUM!</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.803914787199152</v>
+        <v>0.812977206992152</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.184679811508303</v>
+        <v>0.451467318796342</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.7177926264217</v>
+        <v>13.0665828394462</v>
       </c>
       <c r="AG5" t="n">
-        <v>19.1190703603397</v>
+        <v>16.0907886012859</v>
       </c>
       <c r="AH5" t="n">
-        <v>-68.7118798942491</v>
+        <v>-141.756751859305</v>
       </c>
       <c r="AI5" t="n">
-        <v>11.7787880451822</v>
+        <v>6.25876965252231</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.40215323592798</v>
+        <v>2.83700347271074</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.632168110368808</v>
+        <v>-0.296189467230712</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.12649293486599</v>
+        <v>-1.02866412942944</v>
       </c>
       <c r="AM5"/>
       <c r="AN5" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="AO5"/>
       <c r="AP5" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AQ5"/>
       <c r="AR5" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="AS5"/>
       <c r="AT5" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="AU5"/>
       <c r="AV5" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="AW5" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="AX5" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="AY5"/>
       <c r="AZ5" t="n">
         <v>16</v>
       </c>
       <c r="BA5" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="BB5" t="n">
         <v>33</v>
       </c>
       <c r="BC5" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="BD5" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="BE5" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="BF5" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="BG5" t="n">
-        <v>-68.7118798942491</v>
+        <v>-141.756751859305</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.7787880451822</v>
+        <v>6.25876965252231</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.40215323592798</v>
+        <v>2.83700347271074</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.632168110368808</v>
+        <v>-0.296189467230712</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.632168110368808</v>
+        <v>-0.296189467230712</v>
       </c>
       <c r="BL5" t="n">
-        <v>885.197245831413</v>
+        <v>758.542994815252</v>
       </c>
       <c r="BM5" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="BN5" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="BO5" t="n">
-        <v>-226.816450335612</v>
+        <v>-215.414438128014</v>
       </c>
       <c r="BP5" t="n">
-        <v>10.9778486790247</v>
+        <v>10.7352268606284</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.56973977682172</v>
+        <v>2.56208950777438</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.319189568186482</v>
+        <v>-0.330661412222654</v>
       </c>
       <c r="BS5" t="n">
         <v>-0.635612592670827</v>
       </c>
       <c r="BT5"/>
       <c r="BU5" t="n">
-        <v>953.909125725662</v>
+        <v>900.299746674557</v>
       </c>
       <c r="BV5" t="n">
-        <v>727.09267539005</v>
+        <v>684.885308546543</v>
       </c>
       <c r="BW5" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="BX5" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="BY5" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="BZ5" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="CA5" t="n">
         <v>0.159942318730386</v>
@@ -2695,33 +3523,1405 @@
       <c r="CB5" t="n">
         <v>-0.549828150540717</v>
       </c>
-      <c r="CC5"/>
+      <c r="CC5" t="n">
+        <v>1034.26927449641</v>
+      </c>
       <c r="CD5" t="n">
-        <v>885.197245831413</v>
+        <v>939.086523267038</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.930882880695775</v>
-      </c>
-      <c r="CF5"/>
+        <v>75438.3360791748</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>20189.9453783714</v>
+      </c>
       <c r="CG5" t="n">
+        <v>18167.1398585121</v>
+      </c>
+      <c r="CH5"/>
+      <c r="CI5" t="n">
+        <v>0.00893392242952981</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.00811174261902884</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.651629376761968</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.17439888268424</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0.156926075505233</v>
+      </c>
+      <c r="CN5"/>
+      <c r="CO5"/>
+      <c r="CP5" t="n">
+        <v>758.542994815252</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.936856220919352</v>
+      </c>
+      <c r="CR5"/>
+      <c r="CS5" t="n">
         <v>1</v>
       </c>
-      <c r="CH5" t="n">
-        <v>52.0475208353742</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>6.01644008001093</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>0.154614253658224</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>0.371782786276091</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>0.503440314450764</v>
-      </c>
-      <c r="CM5"/>
+      <c r="CT5" t="n">
+        <v>23.9098418316386</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.71498881906665</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0.330424475505496</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0.0117085442418624</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0.423404505479032</v>
+      </c>
+      <c r="CY5"/>
+      <c r="CZ5" t="n">
+        <v>1403.18434928644</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>1222.8294336542</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>61881.7098337291</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>19282.1868101002</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>9994.44911681635</v>
+      </c>
+      <c r="DE5"/>
+      <c r="DF5" t="n">
+        <v>0.016807496425324</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0.0145473306522012</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0.662340612080334</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.215155173177175</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0.0911493876649658</v>
+      </c>
+      <c r="DK5"/>
+      <c r="DL5" t="n">
+        <v>521.724702131946</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>401.273072096738</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>19171.9646963323</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>1283.76447860938</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>11557.9300879872</v>
+      </c>
+      <c r="DQ5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.871389615762453</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11.4515460703471</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.94986951736121</v>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.884339681598727</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11.3539707148221</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.949993912040946</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.871389615762453</v>
+      </c>
+      <c r="S6" t="n">
+        <v>11.4515460703471</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.94986951736121</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.0323815814009366</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.07150905096083</v>
+      </c>
+      <c r="W6"/>
+      <c r="X6" t="n">
+        <v>-213.450960528643</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11.084703098047</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.5620222792153</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.358433500146809</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.612577978411051</v>
+      </c>
+      <c r="AC6" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.85916875073177</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.89009532143615</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10.5929717813917</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9.83924013471976</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-353.356763283176</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>16.8436744142703</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.47451790888165</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.413321647520067</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.499704631346652</v>
+      </c>
+      <c r="AM6"/>
+      <c r="AN6" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO6"/>
+      <c r="AP6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ6"/>
+      <c r="AR6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AS6"/>
+      <c r="AT6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU6"/>
+      <c r="AV6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>151</v>
+      </c>
+      <c r="AY6"/>
+      <c r="AZ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>33</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>152</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-353.356763283176</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>16.8436744142703</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.47451790888165</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0.413321647520067</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0.413321647520067</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>540.135076958623</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>142</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-215.414438128014</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>10.7352268606284</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2.56208950777438</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0.330661412222654</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0.635612592670827</v>
+      </c>
+      <c r="BT6"/>
+      <c r="BU6" t="n">
+        <v>893.491840241799</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>678.077402113785</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>146</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>146</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>147</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>148</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.159942318730386</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0.549828150540717</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>6224.65757864337</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>5987.98232079642</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>78670.6424990995</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>32098.4462530792</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>4530.51341306012</v>
+      </c>
+      <c r="CH6"/>
+      <c r="CI6" t="n">
+        <v>0.0488161566125236</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.0469600582958859</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.616965408381691</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.251728349634051</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.035530027075848</v>
+      </c>
+      <c r="CN6"/>
+      <c r="CO6"/>
+      <c r="CP6" t="n">
+        <v>540.135076958623</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.95053750952639</v>
+      </c>
+      <c r="CR6"/>
+      <c r="CS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>197.856683710156</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>8.14441534072062</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.123749867292766</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.0776235624287955</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.159627018248918</v>
+      </c>
+      <c r="CY6"/>
+      <c r="CZ6" t="n">
+        <v>3283.64768375717</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>3307.49445309456</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>61417.695656696</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>23768.0886488151</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>5712.13969648891</v>
+      </c>
+      <c r="DE6"/>
+      <c r="DF6" t="n">
+        <v>0.0269474192071902</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.0281268705622703</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.635794392177482</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.240275553632351</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.0688557644207072</v>
+      </c>
+      <c r="DK6"/>
+      <c r="DL6" t="n">
+        <v>4159.21608042154</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>3790.78229628051</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>24399.3514154291</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>11780.9047033681</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>1671.07191568151</v>
+      </c>
+      <c r="DQ6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.871389615762453</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11.4515460703471</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.94986951736121</v>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.884339681598727</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11.3539707148221</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.949993912040946</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.871389615762453</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11.4515460703471</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.94986951736121</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.0323815814009366</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.07150905096083</v>
+      </c>
+      <c r="W7"/>
+      <c r="X7" t="n">
+        <v>-213.450960528643</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11.084703098047</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.5620222792153</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.358433500146809</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.612577978411051</v>
+      </c>
+      <c r="AC7" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.885474701231367</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.832131650852676</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11.9558105878111</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14.6344411828471</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-73.5451577741097</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.32573178182375</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>2.64952664954895</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.30354535277355</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.72545132547545</v>
+      </c>
+      <c r="AM7"/>
+      <c r="AN7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AO7"/>
+      <c r="AP7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ7"/>
+      <c r="AR7" t="s">
+        <v>153</v>
+      </c>
+      <c r="AS7"/>
+      <c r="AT7" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU7"/>
+      <c r="AV7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>152</v>
+      </c>
+      <c r="AY7"/>
+      <c r="AZ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>33</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>153</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>151</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-73.5451577741097</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>5.32573178182375</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.64952664954895</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0.30354535277355</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0.30354535277355</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>734.855765371036</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>142</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-215.414438128014</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>10.7352268606284</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>2.56208950777438</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-0.330661412222654</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-0.635612592670827</v>
+      </c>
+      <c r="BT7"/>
+      <c r="BU7" t="n">
+        <v>808.400923145145</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>592.986485017131</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>146</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>146</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>147</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>148</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.159942318730386</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0.549828150540717</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>342.637788870961</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>627.006585392696</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>44164.7488142925</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>15437.731044551</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>6893.7659799177</v>
+      </c>
+      <c r="CH7"/>
+      <c r="CI7" t="n">
+        <v>0.00507868180185684</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.00929368282865476</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.654623375973272</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.22882275763065</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.102181501765566</v>
+      </c>
+      <c r="CN7"/>
+      <c r="CO7"/>
+      <c r="CP7" t="n">
+        <v>734.855765371036</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.954056826574618</v>
+      </c>
+      <c r="CR7"/>
+      <c r="CS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>197.856683710156</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>8.14441534072062</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.123749867292766</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.0776235624287955</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.159627018248918</v>
+      </c>
+      <c r="CY7"/>
+      <c r="CZ7" t="n">
+        <v>3283.64768375717</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>3307.49445309456</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>61417.695656696</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>23768.0886488151</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>5712.13969648891</v>
+      </c>
+      <c r="DE7"/>
+      <c r="DF7" t="n">
+        <v>0.0269474192071902</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.0281268705622703</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.635794392177482</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.240275553632351</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.0688557644207072</v>
+      </c>
+      <c r="DK7"/>
+      <c r="DL7" t="n">
+        <v>4159.21608042154</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>3790.78229628051</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>24399.3514154291</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>11780.9047033681</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>1671.07191568151</v>
+      </c>
+      <c r="DQ7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.440423873164015</v>
+      </c>
+      <c r="K8" t="n">
+        <v>11.7942585414253</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.863696501325677</v>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.884339681598727</v>
+      </c>
+      <c r="O8" t="n">
+        <v>11.3539707148221</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.949993912040946</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.440423873164015</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11.7942585414253</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.863696501325677</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.36660009517524</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.0864535682145</v>
+      </c>
+      <c r="W8"/>
+      <c r="X8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-10.0126091829737</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.52834134419609</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0836992173456869</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.312337866551871</v>
+      </c>
+      <c r="AC8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-8.73661080461327</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-15.6704123929287</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>18.2133080788635</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>18.5303300784971</v>
+      </c>
+      <c r="AH8"/>
+      <c r="AI8"/>
+      <c r="AJ8" t="n">
+        <v>1.3422544533518</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0245729011698342</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.685402927069589</v>
+      </c>
+      <c r="AM8"/>
+      <c r="AN8" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO8"/>
+      <c r="AP8" t="s">
+        <v>155</v>
+      </c>
+      <c r="AQ8"/>
+      <c r="AR8" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS8"/>
+      <c r="AT8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU8"/>
+      <c r="AV8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>157</v>
+      </c>
+      <c r="AY8"/>
+      <c r="AZ8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>132</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>156</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>158</v>
+      </c>
+      <c r="BG8"/>
+      <c r="BH8"/>
+      <c r="BI8" t="n">
+        <v>1.3422544533518</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.0245729011698342</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.0245729011698342</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>750.302162476609</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>159</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>132</v>
+      </c>
+      <c r="BO8"/>
+      <c r="BP8" t="n">
+        <v>-9.70171192168587</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.48932258861972</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.0736631300163193</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0.0472380840245461</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-0.105724727200812</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>750.302162476609</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>750.302162476609</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>160</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>160</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>161</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>162</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0.890552086517798</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.0549760078582728</v>
+      </c>
+      <c r="CC8"/>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>9532.18318227227</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>8.83187916539828</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>6802.11883247592</v>
+      </c>
+      <c r="CH8"/>
+      <c r="CI8"/>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.583253080109818</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0.000540403035472125</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0.416206516854709</v>
+      </c>
+      <c r="CN8"/>
+      <c r="CO8"/>
+      <c r="CP8" t="n">
+        <v>750.302162476609</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.282772261973041</v>
+      </c>
+      <c r="CR8"/>
+      <c r="CS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT8"/>
+      <c r="CU8"/>
+      <c r="CV8" t="n">
+        <v>0.263166604811838</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0.0836172382290505</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0.527593668231697</v>
+      </c>
+      <c r="CY8"/>
+      <c r="CZ8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>1479.10478251605</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>7029.86882199788</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>224.492997950816</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>3418.06051964545</v>
+      </c>
+      <c r="DE8"/>
+      <c r="DF8" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0.185819043083645</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.576023510280182</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.0279183498261087</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.210239096810064</v>
+      </c>
+      <c r="DK8"/>
+      <c r="DL8"/>
+      <c r="DM8" t="n">
+        <v>2091.7700436051</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>3538.806905621</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>304.990879062892</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>4785.78116186626</v>
+      </c>
+      <c r="DQ8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.440423873164015</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11.7942585414253</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.863696501325677</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.884339681598727</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11.3539707148221</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.949993912040946</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.440423873164015</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11.7942585414253</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.863696501325677</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.36660009517524</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.0864535682145</v>
+      </c>
+      <c r="W9"/>
+      <c r="X9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-10.0126091829737</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.52834134419609</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.0836992173456869</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.312337866551871</v>
+      </c>
+      <c r="AC9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.0151178752735728</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.628416390785633</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>7.43148383045613</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.79811769145137</v>
+      </c>
+      <c r="AH9"/>
+      <c r="AI9" t="n">
+        <v>-10.0126091829737</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.71442823504038</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.14282553352154</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.060727193965848</v>
+      </c>
+      <c r="AM9"/>
+      <c r="AN9" t="s">
+        <v>154</v>
+      </c>
+      <c r="AO9"/>
+      <c r="AP9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AQ9"/>
+      <c r="AR9" t="s">
+        <v>163</v>
+      </c>
+      <c r="AS9"/>
+      <c r="AT9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AU9"/>
+      <c r="AV9" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>128</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>158</v>
+      </c>
+      <c r="AY9"/>
+      <c r="AZ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>157</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>163</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>157</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-6.20011218634429</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-10.0126091829737</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.71442823504038</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.14282553352154</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.14282553352154</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>645.467030670798</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>159</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BO9"/>
+      <c r="BP9" t="n">
+        <v>-9.70171192168587</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.48932258861972</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.0736631300163193</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.0472380840245461</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0.105724727200812</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>651.667142857143</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>651.667142857143</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>160</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>161</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>162</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0.890552086517798</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.0549760078582728</v>
+      </c>
+      <c r="CC9"/>
+      <c r="CD9" t="n">
+        <v>2958.20956503209</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>4527.55446172349</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>440.154116736233</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>34.0022068149883</v>
+      </c>
+      <c r="CH9"/>
+      <c r="CI9"/>
+      <c r="CJ9" t="n">
+        <v>0.371638086167291</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.568793940450545</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.0552962966167454</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.00427167676541861</v>
+      </c>
+      <c r="CN9"/>
+      <c r="CO9"/>
+      <c r="CP9"/>
+      <c r="CQ9" t="n">
+        <v>0.927582644465118</v>
+      </c>
+      <c r="CR9"/>
+      <c r="CS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT9"/>
+      <c r="CU9"/>
+      <c r="CV9" t="n">
+        <v>0.263166604811838</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.0836172382290505</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.527593668231697</v>
+      </c>
+      <c r="CY9"/>
+      <c r="CZ9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1479.10478251605</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>7029.86882199788</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>224.492997950816</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>3418.06051964545</v>
+      </c>
+      <c r="DE9"/>
+      <c r="DF9" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.185819043083645</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.576023510280182</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.0279183498261087</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.210239096810064</v>
+      </c>
+      <c r="DK9"/>
+      <c r="DL9"/>
+      <c r="DM9" t="n">
+        <v>2091.7700436051</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>3538.806905621</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>304.990879062892</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>4785.78116186626</v>
+      </c>
+      <c r="DQ9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
